--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\Documents\УЧЕБА\System Design 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F24E390-209F-4351-BE1B-5A0B56EFABF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82D9D0A-E9EB-438D-9C48-4F6E87DB755D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
@@ -19,9 +19,10 @@
     <sheet name="Kafka" sheetId="4" r:id="rId4"/>
     <sheet name="OLTP" sheetId="5" r:id="rId5"/>
     <sheet name="Гео-поиск" sheetId="6" r:id="rId6"/>
+    <sheet name="Расчет параметров" sheetId="7" r:id="rId7"/>
+    <sheet name="Расчет ресурсов" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="105">
   <si>
     <t>Категория пользователей</t>
   </si>
@@ -137,9 +138,6 @@
     <t>Операции чтения (GET), RPS</t>
   </si>
   <si>
-    <t>Операции записи в кеш (SET/INCR), TPS</t>
-  </si>
-  <si>
     <t>Размер типичного ключа, байт</t>
   </si>
   <si>
@@ -269,20 +267,221 @@
   <si>
     <t>Операций чтения из Гео-индекс</t>
   </si>
+  <si>
+    <t>Пиковая нагрузка</t>
+  </si>
+  <si>
+    <t>Допущение</t>
+  </si>
+  <si>
+    <t>Расчет</t>
+  </si>
+  <si>
+    <t>Итог</t>
+  </si>
+  <si>
+    <t>Сервис Запросов</t>
+  </si>
+  <si>
+    <t>Загрузчик моделей чтения</t>
+  </si>
+  <si>
+    <t>Сервис резервирования</t>
+  </si>
+  <si>
+    <t>Гео-сервис</t>
+  </si>
+  <si>
+    <t>1 instance = ~1 000 RPS</t>
+  </si>
+  <si>
+    <t>OPS</t>
+  </si>
+  <si>
+    <t>MPS</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>TPS</t>
+  </si>
+  <si>
+    <t>RPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фактор резерва </t>
+  </si>
+  <si>
+    <t>мультиплаикатор, ключей</t>
+  </si>
+  <si>
+    <t>Принимаем</t>
+  </si>
+  <si>
+    <t>1 master node = до 
+8 000–10 000 OPS</t>
+  </si>
+  <si>
+    <t>Фактор
+резерва</t>
+  </si>
+  <si>
+    <t>Инстансов</t>
+  </si>
+  <si>
+    <t>Узлов</t>
+  </si>
+  <si>
+    <t>Партиций</t>
+  </si>
+  <si>
+    <t>10-12</t>
+  </si>
+  <si>
+    <r>
+      <t>Распределенный кеш</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Redis)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Event Bus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> (Kafka)</t>
+    </r>
+  </si>
+  <si>
+    <t>1 инстанс = 2 000–3 000 RPS</t>
+  </si>
+  <si>
+    <t>1 партиция = 500–1 000 MPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = 400–600 EPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = 150–250 TPS</t>
+  </si>
+  <si>
+    <t>3–5</t>
+  </si>
+  <si>
+    <t>7–8</t>
+  </si>
+  <si>
+    <t>9-10</t>
+  </si>
+  <si>
+    <t>Компонент</t>
+  </si>
+  <si>
+    <t>CPU (cores)</t>
+  </si>
+  <si>
+    <t>RAM (GB)</t>
+  </si>
+  <si>
+    <t>Итого CPU</t>
+  </si>
+  <si>
+    <t>Итого RAM</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Запас (+30%)</t>
+  </si>
+  <si>
+    <t>Инстансы</t>
+  </si>
+  <si>
+    <t>Сервис запросов</t>
+  </si>
+  <si>
+    <t>Сервис резерва</t>
+  </si>
+  <si>
+    <t>Сервис комманд</t>
+  </si>
+  <si>
+    <t>Адаптеры (POS/WMS/OMS)</t>
+  </si>
+  <si>
+    <t>Распределенный кеш</t>
+  </si>
+  <si>
+    <t>- мастер-ноды</t>
+  </si>
+  <si>
+    <t>- реплики</t>
+  </si>
+  <si>
+    <t>PostgreSQL Хранилища событий</t>
+  </si>
+  <si>
+    <t>- мастер</t>
+  </si>
+  <si>
+    <t>Kafka</t>
+  </si>
+  <si>
+    <t>SSD (TB)</t>
+  </si>
+  <si>
+    <t>Итого SSD</t>
+  </si>
+  <si>
+    <t>- брокеры</t>
+  </si>
+  <si>
+    <t>Хранилище модели чтения (MongoDB)</t>
+  </si>
+  <si>
+    <t>Оценка write IOPS (верхняя граница)</t>
+  </si>
+  <si>
+    <t>Требование к задержке fsync</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент hot SKU </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="#,##0.0"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +525,12 @@
       <sz val="11"/>
       <name val="Inherit"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -335,12 +540,38 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -349,29 +580,57 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -693,26 +952,29 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="66.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" customWidth="1"/>
-    <col min="3" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3" t="s">
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
@@ -774,7 +1036,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="15.75" thickBot="1">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -818,7 +1080,7 @@
         <f t="shared" si="0"/>
         <v>7.1556350626118068E-3</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="11">
         <f>C5/B5</f>
         <v>100</v>
       </c>
@@ -829,12 +1091,12 @@
         <f t="shared" si="2"/>
         <v>7.1942446043165471E-3</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="11">
         <f>F5/B5</f>
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" ht="15.75" thickBot="1">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -842,14 +1104,25 @@
         <f>SUM(C2:C5)</f>
         <v>83850</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="12">
+        <f>SUM(E2:E4)</f>
+        <v>10000</v>
+      </c>
       <c r="F6" s="2">
         <f>SUM(F2:F5)</f>
         <v>417000</v>
       </c>
+      <c r="H6" s="12">
+        <f>SUM(H2:H4)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="E7" s="10"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="E16" s="4"/>
+      <c r="E16" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -878,21 +1151,21 @@
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="5">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4">
         <v>10000</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>50000</v>
       </c>
     </row>
@@ -911,18 +1184,18 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <f>B2*B3</f>
         <v>8500</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <f>C2*C3</f>
         <v>42500</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="6" t="s">
-        <v>16</v>
+      <c r="A5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -932,13 +1205,13 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4">
         <v>1000</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>5000</v>
       </c>
     </row>
@@ -946,13 +1219,11 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5">
-        <f>B6+B5</f>
-        <v>1100</v>
-      </c>
-      <c r="C7" s="5">
-        <f>C5+C6</f>
-        <v>5500</v>
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -960,57 +1231,57 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>200</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C9">
-        <v>200</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="B10">
-        <v>1.1000000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="C10">
-        <v>1.1000000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="7">
-        <f>B4*(B8+B9)*B10/1024^2</f>
-        <v>2.140045166015625</v>
-      </c>
-      <c r="C11" s="7">
-        <f>C4*(C8+C9)*C10/1024^2</f>
-        <v>10.700225830078125</v>
+        <v>13</v>
+      </c>
+      <c r="B11" s="6">
+        <f>B4*B10*(B7+B8)*B9/1024^2</f>
+        <v>3.7450790405273442</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C4*C10*(C7+C8)*C9/1024^2</f>
+        <v>21.40045166015625</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="7">
-        <f>B7*(B8+B9)*B10/1024^2</f>
+        <v>14</v>
+      </c>
+      <c r="B12" s="6">
+        <f>(B5+B6)*(B7+B8)*B9/1024^2</f>
         <v>0.276947021484375</v>
       </c>
-      <c r="C12" s="7">
-        <f>C7*(C8+C9)*C10/1024^2</f>
+      <c r="C12" s="6">
+        <f>(C5+C6)*(C7+C8)*C9/1024^2</f>
         <v>1.3847351074218752</v>
       </c>
     </row>
@@ -1022,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF55EE5-F96B-41B5-BBCA-C26C1C7AFB6E}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" bestFit="1" customWidth="1"/>
@@ -1034,72 +1305,94 @@
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="5">
+        <v>21</v>
+      </c>
+      <c r="B2" s="4">
         <v>1000</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="5">
+        <v>22</v>
+      </c>
+      <c r="B3" s="4">
         <v>500</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="9">
+        <v>23</v>
+      </c>
+      <c r="B4" s="8">
         <f>B2*B3/1024^2</f>
         <v>0.476837158203125</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <f>C2*C3/1024^2</f>
         <v>2.384185791015625</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="9">
+        <v>24</v>
+      </c>
+      <c r="B5" s="8">
         <f>B4*24*3600/1024</f>
         <v>40.233135223388672</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <f>C4*24*3600/1024</f>
         <v>201.16567611694336</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="5">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4">
         <f>B2/10</f>
         <v>100</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <f>C2/10</f>
         <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8">
+        <v>1000</v>
+      </c>
+      <c r="C8">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
@@ -1122,27 +1415,27 @@
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="5">
+        <v>26</v>
+      </c>
+      <c r="B2" s="4">
         <v>1000</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1153,20 +1446,20 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="5">
+        <v>28</v>
+      </c>
+      <c r="B4" s="4">
         <f>B2*B3</f>
         <v>3000</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <f>C2*C3</f>
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1177,7 +1470,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>1.4</v>
@@ -1187,8 +1480,8 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6" t="s">
-        <v>32</v>
+      <c r="A7" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="B7">
         <f>B4*B5/1000*B6</f>
@@ -1200,8 +1493,8 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="6" t="s">
-        <v>31</v>
+      <c r="A8" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1212,13 +1505,13 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="5">
+        <v>29</v>
+      </c>
+      <c r="B9" s="4">
         <f>B2*B8</f>
         <v>4000</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <f>C2*C8</f>
         <v>20000</v>
       </c>
@@ -1234,7 +1527,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1243,102 +1536,102 @@
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="5">
+        <v>34</v>
+      </c>
+      <c r="C2" s="4">
         <v>100</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0.5</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <f>C2*$B3</f>
         <v>50</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <f>D2*$B3</f>
         <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <f>C2*$B4</f>
         <v>200</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <f>D2*$B4</f>
         <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="A5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="21">
         <v>3</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="21"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <f>C2*$B6*$C5</f>
         <v>1500</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <f>D2*$B6*$C5</f>
         <v>7500</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="3">
+        <v>40</v>
+      </c>
+      <c r="C7" s="21">
         <v>400</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="21"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>15</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <f>C2*$C7*$B8*60/1024^2</f>
         <v>34.332275390625</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <f>D2*$C7*$B8*60/1024^2</f>
         <v>171.661376953125</v>
       </c>
@@ -1358,7 +1651,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1367,97 +1660,97 @@
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="5">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4">
         <v>10000</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>50000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="12">
+        <v>44</v>
+      </c>
+      <c r="C3" s="22">
         <v>0.1</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="23"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="5">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4">
         <f>C2*$C3</f>
         <v>1000</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <f>D2*$C3</f>
         <v>5000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="3">
+        <v>42</v>
+      </c>
+      <c r="C5" s="21">
         <v>200</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="21"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="5">
+        <v>45</v>
+      </c>
+      <c r="C6" s="4">
         <f>C4*$C5/1000</f>
         <v>200</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <f>D4*$C5/1000</f>
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4">
         <f>C4*$B7</f>
-        <v>1000</v>
-      </c>
-      <c r="D7" s="5">
+        <v>4000</v>
+      </c>
+      <c r="D7" s="4">
         <f>D4*$B7</f>
-        <v>5000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>20</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <f>C4*$B8</f>
         <v>20000</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <f>D4*$B8</f>
         <v>100000</v>
       </c>
@@ -1470,4 +1763,655 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEACBF24-690E-480A-A550-EDA8CDE0ADBA}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30">
+      <c r="B1" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="24"/>
+      <c r="D1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="13"/>
+      <c r="H1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="14">
+        <v>50000</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="14">
+        <v>2500</v>
+      </c>
+      <c r="F2" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="16">
+        <f>B2/E2*F2</f>
+        <v>30</v>
+      </c>
+      <c r="I2" s="14">
+        <f>H2</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30">
+      <c r="A3" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="14">
+        <v>42500</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="14">
+        <v>8000</v>
+      </c>
+      <c r="F3" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="16">
+        <f>(B3+B4)/E3*F3</f>
+        <v>9</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="25"/>
+      <c r="B4" s="14">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="14">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="14">
+        <v>800</v>
+      </c>
+      <c r="F5" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="16">
+        <f>B5/E5*F5</f>
+        <v>8.125</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="25"/>
+      <c r="B6" s="14">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="14">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="14">
+        <v>500</v>
+      </c>
+      <c r="F7" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="16">
+        <f>B7/E7*F7</f>
+        <v>12</v>
+      </c>
+      <c r="I7" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="14">
+        <v>500</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="14">
+        <v>200</v>
+      </c>
+      <c r="F8" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="16">
+        <f>B8/E8*F8</f>
+        <v>3.75</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="14">
+        <v>5000</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="16">
+        <f>B9/E9*F9</f>
+        <v>6.5</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="25"/>
+      <c r="B10" s="14">
+        <v>20</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C10:D10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F55A25-67AE-4582-B6E5-DF4CB5C7DF4D}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="126.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>120</v>
+      </c>
+      <c r="F2">
+        <f>B2*E2</f>
+        <v>240</v>
+      </c>
+      <c r="G2">
+        <f t="shared" ref="G2:G7" si="0">C2*E2</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F10" si="1">B3*E3</f>
+        <v>40</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>15</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f>C9*E9</f>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>64</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f>C10*E10</f>
+        <v>512</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>64</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <f t="shared" ref="F12" si="2">B12*E12</f>
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <f>C12*E12</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>32</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <f t="shared" ref="F13" si="3">B13*E13</f>
+        <v>24</v>
+      </c>
+      <c r="G13">
+        <f>C13*E13</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <f t="shared" ref="F15" si="4">B15*E15</f>
+        <v>96</v>
+      </c>
+      <c r="G15">
+        <f>C15*E15</f>
+        <v>192</v>
+      </c>
+      <c r="H15">
+        <f>D15*E15</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>0.5</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <f t="shared" ref="F16" si="5">B16*E16</f>
+        <v>24</v>
+      </c>
+      <c r="G16">
+        <f>C16*E16</f>
+        <v>48</v>
+      </c>
+      <c r="H16">
+        <f>D16*E16</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="20"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20:F20" si="6">SUM(E2:E19)</f>
+        <v>202</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="6"/>
+        <v>514</v>
+      </c>
+      <c r="G20">
+        <f>SUM(G2:G19)</f>
+        <v>1876</v>
+      </c>
+      <c r="H20">
+        <f>SUM(H2:H19)</f>
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21">
+        <f>ROUNDUP(F20*1.3,0)</f>
+        <v>669</v>
+      </c>
+      <c r="G21">
+        <f>ROUNDUP(G20*1.3,0)</f>
+        <v>2439</v>
+      </c>
+      <c r="H21">
+        <f>ROUNDUP(H20*1.3,0)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16.5">
+      <c r="L24" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\Documents\УЧЕБА\System Design 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82D9D0A-E9EB-438D-9C48-4F6E87DB755D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F014613-D9AD-49C8-8029-E84AD574E5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Нагрузка по категориям" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="120">
   <si>
     <t>Категория пользователей</t>
   </si>
@@ -135,9 +135,6 @@
     <t>Коэффициент попаданий в кэш (целевой)</t>
   </si>
   <si>
-    <t>Операции чтения (GET), RPS</t>
-  </si>
-  <si>
     <t>Размер типичного ключа, байт</t>
   </si>
   <si>
@@ -193,19 +190,7 @@
     <t>Объем за сутки, ГБ</t>
   </si>
   <si>
-    <t>Требование к IOPS (write)</t>
-  </si>
-  <si>
-    <t>Скорость поступления сообщений в систему (inventory.events), msg/s</t>
-  </si>
-  <si>
     <t>Коэффициент репликации</t>
-  </si>
-  <si>
-    <t>Фактическая запись на диски, msg/s</t>
-  </si>
-  <si>
-    <t>Суммарная скорость чтения (всех consumer-групп), msg/s</t>
   </si>
   <si>
     <t>Consumer groups (потребители)</t>
@@ -334,24 +319,6 @@
   </si>
   <si>
     <t>Партиций</t>
-  </si>
-  <si>
-    <t>10-12</t>
-  </si>
-  <si>
-    <r>
-      <t>Распределенный кеш</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t> (Redis)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -381,15 +348,6 @@
     <t>1 инстанс = 150–250 TPS</t>
   </si>
   <si>
-    <t>3–5</t>
-  </si>
-  <si>
-    <t>7–8</t>
-  </si>
-  <si>
-    <t>9-10</t>
-  </si>
-  <si>
     <t>Компонент</t>
   </si>
   <si>
@@ -408,9 +366,6 @@
     <t>Итого</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Запас (+30%)</t>
   </si>
   <si>
@@ -438,9 +393,6 @@
     <t>- реплики</t>
   </si>
   <si>
-    <t>PostgreSQL Хранилища событий</t>
-  </si>
-  <si>
     <t>- мастер</t>
   </si>
   <si>
@@ -453,19 +405,100 @@
     <t>Итого SSD</t>
   </si>
   <si>
-    <t>- брокеры</t>
-  </si>
-  <si>
     <t>Хранилище модели чтения (MongoDB)</t>
   </si>
   <si>
-    <t>Оценка write IOPS (верхняя граница)</t>
-  </si>
-  <si>
     <t>Требование к задержке fsync</t>
   </si>
   <si>
     <t xml:space="preserve">Коэффициент hot SKU </t>
+  </si>
+  <si>
+    <t>Конфликты активных блокировок в Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Массовый одновременный запрос популярных SKU, ключей </t>
+  </si>
+  <si>
+    <t>Коэффициент эксплуатационного запаса</t>
+  </si>
+  <si>
+    <t>Коэффициент событий на один пользовательский запрос</t>
+  </si>
+  <si>
+    <t>Расчетный поток событий (EPS)</t>
+  </si>
+  <si>
+    <t>Доля событий, приводящих к записи в Redis</t>
+  </si>
+  <si>
+    <t>Оценка write IOPS (верхняя граница, без учета group commit)</t>
+  </si>
+  <si>
+    <t>Примечание : IOPS не выводится напрямую из EPS; основным показателем является поток WAL и latency fsync</t>
+  </si>
+  <si>
+    <t>Распределенный кэш Redis (read + write)</t>
+  </si>
+  <si>
+    <t>9-12</t>
+  </si>
+  <si>
+    <t>Worst-case Redis (hot SKU + burst)</t>
+  </si>
+  <si>
+    <t>Дополнительный burst 30% поверх нагрузки hot SKU</t>
+  </si>
+  <si>
+    <t>Worst-case нагрузка (Read), RPS</t>
+  </si>
+  <si>
+    <t>Примечание по единицам измерения</t>
+  </si>
+  <si>
+    <t>RPS — пользовательские запросы в секунду</t>
+  </si>
+  <si>
+    <t>TPS — бизнес-транзакции в секунду</t>
+  </si>
+  <si>
+    <t>EPS / msg/s — события в секунду</t>
+  </si>
+  <si>
+    <t>OPS — операции в секунду на инфраструктурный компонент</t>
+  </si>
+  <si>
+    <t>Операции чтения Redis, OPS</t>
+  </si>
+  <si>
+    <t>Реальная нагрузка Redis (read), OPS</t>
+  </si>
+  <si>
+    <t>Скорость поступления сообщений в систему (inventory.events), MPS</t>
+  </si>
+  <si>
+    <t>Фактическая запись на диски, MPS</t>
+  </si>
+  <si>
+    <t>Суммарная скорость чтения (всех consumer-групп), MPS</t>
+  </si>
+  <si>
+    <t>Суммарная эксплуатационная нагрузка, MPS</t>
+  </si>
+  <si>
+    <t>- брокеры (для 9–12 партиций)</t>
+  </si>
+  <si>
+    <t>Конфигурация принята исходя из требований отказоустойчивости, а не только из расчетной TPS-нагрузки</t>
+  </si>
+  <si>
+    <t>Количество брокеров определено исходя из 9–12 партиций и replication factor</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>PostgreSQL хранилища событий (конфигурация отказоустойчивости)</t>
   </si>
 </sst>
 </file>
@@ -532,12 +565,18 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -580,7 +619,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -604,16 +643,14 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -632,6 +669,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1118,8 +1175,27 @@
       </c>
     </row>
     <row r="7" spans="1:8">
+      <c r="A7" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="28">
+        <v>0.1</v>
+      </c>
       <c r="E7" s="10"/>
       <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="29">
+        <f>E6*B7</f>
+        <v>1000</v>
+      </c>
+      <c r="H8" s="29">
+        <f>H6*B7</f>
+        <v>5000</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="E16" s="3"/>
@@ -1139,10 +1215,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D177B4C-98B6-45DE-86CF-3985BDBE0E2C}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1152,15 +1228,15 @@
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="4">
         <v>10000</v>
@@ -1181,8 +1257,8 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>10</v>
+      <c r="A4" s="28" t="s">
+        <v>109</v>
       </c>
       <c r="B4" s="4">
         <f>B2*B3</f>
@@ -1194,95 +1270,134 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
+      <c r="A5" t="s">
+        <v>90</v>
       </c>
       <c r="B5">
+        <v>1.75</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="4">
+        <f>B4*B5</f>
+        <v>14875</v>
+      </c>
+      <c r="C6" s="4">
+        <f>C4*C5</f>
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="32">
+        <f>B6*1.3</f>
+        <v>19337.5</v>
+      </c>
+      <c r="C7" s="32">
+        <f>C6*1.3</f>
+        <v>110500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
         <v>100</v>
       </c>
-      <c r="C5">
+      <c r="C8">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="4">
+    <row r="9" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <f>'Нагрузка по категориям'!E8</f>
         <v>1000</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C9" s="4">
+        <f>'Нагрузка по категориям'!H8</f>
         <v>5000</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7">
-        <v>40</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8">
-        <v>200</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C9">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10">
-        <v>1.75</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
+      <c r="A10" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="28">
+        <v>0.8</v>
+      </c>
+      <c r="C10" s="28">
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="6">
-        <f>B4*B10*(B7+B8)*B9/1024^2</f>
-        <v>3.7450790405273442</v>
-      </c>
-      <c r="C11" s="6">
-        <f>C4*C10*(C7+C8)*C9/1024^2</f>
-        <v>21.40045166015625</v>
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="6">
-        <f>(B5+B6)*(B7+B8)*B9/1024^2</f>
-        <v>0.276947021484375</v>
-      </c>
-      <c r="C12" s="6">
-        <f>(C5+C6)*(C7+C8)*C9/1024^2</f>
-        <v>1.3847351074218752</v>
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>200</v>
+      </c>
+      <c r="C12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C13">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6">
+        <f>B6*(B11+B12)*B13/1024^2</f>
+        <v>3.7450790405273442</v>
+      </c>
+      <c r="C14" s="6">
+        <f>C6*(C11+C12)*C13/1024^2</f>
+        <v>21.40045166015625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="27">
+        <f>(B8+B9*B10)*(B11+B12)*B13/1024^2</f>
+        <v>0.22659301757812503</v>
+      </c>
+      <c r="C15" s="27">
+        <f>(C8+C9*C10)*(C11+C12)*C13/1024^2</f>
+        <v>1.132965087890625</v>
       </c>
     </row>
   </sheetData>
@@ -1296,7 +1411,7 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1306,26 +1421,28 @@
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4">
+        <f>'Нагрузка по категориям'!E8</f>
         <v>1000</v>
       </c>
       <c r="C2" s="4">
+        <f>'Нагрузка по категориям'!H8</f>
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="4">
         <v>500</v>
@@ -1336,7 +1453,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="8">
         <f>B2*B3/1024^2</f>
@@ -1349,7 +1466,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="8">
         <f>B4*24*3600/1024</f>
@@ -1361,21 +1478,19 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4">
-        <f>B2/10</f>
-        <v>100</v>
-      </c>
-      <c r="C6" s="4">
-        <f>C2/10</f>
-        <v>500</v>
+      <c r="A6" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="32">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="32">
+        <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1384,14 +1499,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8">
+    <row r="8" spans="1:3" ht="30">
+      <c r="A8" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="28">
         <v>1000</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="28">
         <v>5000</v>
       </c>
     </row>
@@ -1403,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD75DDA6-059A-4502-BE2D-86DB28348AE5}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="66.5703125" bestFit="1" customWidth="1"/>
@@ -1416,26 +1531,28 @@
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>26</v>
+      <c r="A2" s="28" t="s">
+        <v>111</v>
       </c>
       <c r="B2" s="4">
+        <f>'Нагрузка по категориям'!E8</f>
         <v>1000</v>
       </c>
       <c r="C2" s="4">
+        <f>'Нагрузка по категориям'!H8</f>
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -1445,8 +1562,8 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>28</v>
+      <c r="A4" s="28" t="s">
+        <v>112</v>
       </c>
       <c r="B4" s="4">
         <f>B2*B3</f>
@@ -1459,7 +1576,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1470,7 +1587,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>1.4</v>
@@ -1481,7 +1598,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B7">
         <f>B4*B5/1000*B6</f>
@@ -1494,7 +1611,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -1504,8 +1621,8 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>29</v>
+      <c r="A9" s="28" t="s">
+        <v>113</v>
       </c>
       <c r="B9" s="4">
         <f>B2*B8</f>
@@ -1516,14 +1633,39 @@
         <v>20000</v>
       </c>
     </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10">
+        <v>1.3</v>
+      </c>
+      <c r="C10">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="4">
+        <f>B9*B10</f>
+        <v>5200</v>
+      </c>
+      <c r="C11" s="4">
+        <f>C9*C10</f>
+        <v>30000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90B9EB8-A39B-4A01-BF8C-361CA874547E}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.85546875" bestFit="1" customWidth="1"/>
@@ -1537,15 +1679,15 @@
         <v>8</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C2" s="4">
         <v>100</v>
@@ -1556,7 +1698,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>0.5</v>
@@ -1572,7 +1714,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -1588,7 +1730,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="9" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C5" s="21">
         <v>3</v>
@@ -1597,7 +1739,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1613,44 +1755,69 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="21">
-        <v>400</v>
-      </c>
-      <c r="D7" s="21"/>
+        <v>90</v>
+      </c>
+      <c r="C7">
+        <v>1.75</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8" s="4">
+        <f>C6*C7</f>
+        <v>2625</v>
+      </c>
+      <c r="D8" s="4">
+        <f>D6*D7</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="21">
+        <v>400</v>
+      </c>
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
         <v>15</v>
       </c>
-      <c r="C8" s="8">
-        <f>C2*$C7*$B8*60/1024^2</f>
+      <c r="C10" s="8">
+        <f>C2*$C9*$B10*60/1024^2</f>
         <v>34.332275390625</v>
       </c>
-      <c r="D8" s="8">
-        <f>D2*$C7*$B8*60/1024^2</f>
+      <c r="D10" s="8">
+        <f>D2*$C9*$B10*60/1024^2</f>
         <v>171.661376953125</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C9:D9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E5FB74-ABB6-4177-82BB-7F65B8A9C27A}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" bestFit="1" customWidth="1"/>
@@ -1661,15 +1828,15 @@
         <v>8</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="4">
@@ -1681,7 +1848,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C3" s="22">
         <v>0.1</v>
@@ -1690,7 +1857,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C4" s="4">
         <f>C2*$C3</f>
@@ -1703,7 +1870,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C5" s="21">
         <v>200</v>
@@ -1712,7 +1879,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4">
         <f>C4*$C5/1000</f>
@@ -1725,7 +1892,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -1741,7 +1908,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -1753,6 +1920,30 @@
       <c r="D8" s="4">
         <f>D4*$B8</f>
         <v>100000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9">
+        <v>1.75</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="4">
+        <f>C8*C9</f>
+        <v>35000</v>
+      </c>
+      <c r="D10" s="4">
+        <f>D8*D9</f>
+        <v>200000</v>
       </c>
     </row>
   </sheetData>
@@ -1767,11 +1958,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEACBF24-690E-480A-A550-EDA8CDE0ADBA}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
@@ -1779,42 +1970,43 @@
     <col min="7" max="7" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30">
+    <row r="1" spans="1:10" ht="30">
       <c r="B1" s="24" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G1" s="13"/>
       <c r="H1" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B2" s="14">
         <v>50000</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E2" s="14">
         <v>2500</v>
@@ -1823,7 +2015,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H2" s="16">
         <f>B2/E2*F2</f>
@@ -1834,188 +2026,242 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30">
-      <c r="A3" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="14">
-        <v>42500</v>
+    <row r="3" spans="1:10" ht="30">
+      <c r="A3" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="19">
+        <v>85000</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="14">
-        <v>8000</v>
+        <v>59</v>
+      </c>
+      <c r="E3" s="19">
+        <v>9000</v>
       </c>
       <c r="F3" s="15">
         <v>1.5</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H3" s="16">
         <f>(B3+B4)/E3*F3</f>
-        <v>9</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="25"/>
+        <v>15.083333333333332</v>
+      </c>
+      <c r="I3" s="20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="30"/>
       <c r="B4" s="14">
         <v>5500</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="14">
+    <row r="5" spans="1:10" ht="30">
+      <c r="A5" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="29">
+        <f>B3*1.3</f>
+        <v>110500</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="19">
+        <v>9000</v>
+      </c>
+      <c r="F5" s="36">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="37">
+        <f>(B5+B6)/E5*F5</f>
+        <v>19.25</v>
+      </c>
+      <c r="I5" s="20">
+        <v>20</v>
+      </c>
+      <c r="J5" s="35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="14">
         <v>5000</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="C6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="14">
         <v>800</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F6" s="15">
         <v>1.3</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="16">
-        <f>B5/E5*F5</f>
+      <c r="G6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="16">
+        <f>B6/E6*F6</f>
         <v>8.125</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="25"/>
-      <c r="B6" s="14">
+      <c r="I6" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="30"/>
+      <c r="B7" s="14">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="14">
+        <v>5000</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="14">
+        <v>500</v>
+      </c>
+      <c r="F8" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="14">
-        <v>5000</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="14">
-        <v>500</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1.2</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="16">
-        <f>B7/E7*F7</f>
-        <v>12</v>
-      </c>
-      <c r="I7" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="14">
-        <v>500</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="14">
-        <v>200</v>
-      </c>
-      <c r="F8" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="H8" s="16">
         <f>B8/E8*F8</f>
-        <v>3.75</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="14">
+        <v>500</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="14">
-        <v>5000</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E9" s="14">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="F9" s="15">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H9" s="16">
         <f>B9/E9*F9</f>
+        <v>3.75</v>
+      </c>
+      <c r="I9" s="34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="14">
+        <v>5000</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="16">
+        <f>B10/E10*F10</f>
         <v>6.5</v>
       </c>
-      <c r="I9" s="18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="25"/>
-      <c r="B10" s="14">
+      <c r="I10" s="34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="25"/>
+      <c r="B11" s="14">
         <v>20</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="26"/>
+      <c r="C11" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="26"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="28" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="28" t="s">
+        <v>108</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C11:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2024,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F55A25-67AE-4582-B6E5-DF4CB5C7DF4D}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -2035,38 +2281,39 @@
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="99.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="126.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -2074,21 +2321,29 @@
       <c r="C2">
         <v>4</v>
       </c>
+      <c r="D2" s="28">
+        <v>0.05</v>
+      </c>
       <c r="E2">
-        <v>120</v>
+        <f>'Расчет параметров'!I2</f>
+        <v>30</v>
       </c>
       <c r="F2">
         <f>B2*E2</f>
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <f t="shared" ref="G2:G7" si="0">C2*E2</f>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>120</v>
+      </c>
+      <c r="H2" s="28">
+        <f t="shared" ref="H2:H14" si="1">D2*E2</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -2096,21 +2351,29 @@
       <c r="C3">
         <v>8</v>
       </c>
+      <c r="D3" s="28">
+        <v>0.1</v>
+      </c>
       <c r="E3">
-        <v>10</v>
+        <f>'Расчет параметров'!I9</f>
+        <v>4</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F10" si="1">B3*E3</f>
-        <v>40</v>
+        <f t="shared" ref="F3:F10" si="2">B3*E3</f>
+        <v>16</v>
       </c>
       <c r="G3">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>32</v>
+      </c>
+      <c r="H3" s="28">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -2118,21 +2381,28 @@
       <c r="C4">
         <v>4</v>
       </c>
+      <c r="D4" s="28">
+        <v>0.05</v>
+      </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4" s="28">
+        <f t="shared" si="1"/>
+        <v>0.30000000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -2140,21 +2410,29 @@
       <c r="C5">
         <v>4</v>
       </c>
+      <c r="D5" s="28">
+        <v>0.1</v>
+      </c>
       <c r="E5">
-        <v>15</v>
+        <f>'Расчет параметров'!I8</f>
+        <v>12</v>
       </c>
       <c r="F5">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f t="shared" si="2"/>
+        <v>24</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>48</v>
+      </c>
+      <c r="H5" s="28">
+        <f t="shared" si="1"/>
+        <v>1.2000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2162,21 +2440,29 @@
       <c r="C6">
         <v>4</v>
       </c>
+      <c r="D6" s="28">
+        <v>0.05</v>
+      </c>
       <c r="E6">
-        <v>10</v>
+        <f>'Расчет параметров'!I10</f>
+        <v>7</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>14</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>28</v>
+      </c>
+      <c r="H6" s="28">
+        <f t="shared" si="1"/>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -2184,69 +2470,100 @@
       <c r="C7">
         <v>2</v>
       </c>
+      <c r="D7" s="28">
+        <v>0.05</v>
+      </c>
       <c r="E7">
         <v>12</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="28">
+        <f t="shared" si="1"/>
+        <v>0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="20" t="s">
-        <v>93</v>
+        <v>81</v>
+      </c>
+      <c r="D8" s="28"/>
+      <c r="H8" s="28"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
       </c>
       <c r="C9">
         <v>32</v>
       </c>
+      <c r="D9" s="28">
+        <v>0.2</v>
+      </c>
       <c r="E9">
         <v>8</v>
       </c>
       <c r="F9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>32</v>
       </c>
       <c r="G9">
         <f>C9*E9</f>
         <v>256</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="20" t="s">
-        <v>94</v>
+      <c r="H9" s="28">
+        <f t="shared" si="1"/>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
       </c>
       <c r="C10">
         <v>64</v>
       </c>
+      <c r="D10" s="28">
+        <v>0.2</v>
+      </c>
       <c r="E10">
         <v>8</v>
       </c>
       <c r="F10">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>32</v>
       </c>
       <c r="G10">
         <f>C10*E10</f>
         <v>512</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="20" t="s">
-        <v>96</v>
+      <c r="H10" s="28">
+        <f t="shared" si="1"/>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="H11" s="28"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="18" t="s">
+        <v>84</v>
       </c>
       <c r="B12">
         <v>16</v>
@@ -2254,21 +2571,31 @@
       <c r="C12">
         <v>64</v>
       </c>
+      <c r="D12" s="28">
+        <v>2</v>
+      </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <f t="shared" ref="F12" si="2">B12*E12</f>
+        <f t="shared" ref="F12" si="3">B12*E12</f>
         <v>16</v>
       </c>
       <c r="G12">
         <f>C12*E12</f>
         <v>64</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="20" t="s">
-        <v>94</v>
+      <c r="H12" s="28">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -2276,26 +2603,33 @@
       <c r="C13">
         <v>32</v>
       </c>
+      <c r="D13" s="28">
+        <v>2</v>
+      </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13">
-        <f t="shared" ref="F13" si="3">B13*E13</f>
+        <f t="shared" ref="F13" si="4">B13*E13</f>
         <v>24</v>
       </c>
       <c r="G13">
         <f>C13*E13</f>
         <v>96</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="20" t="s">
-        <v>100</v>
+      <c r="H13" s="28">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>115</v>
       </c>
       <c r="B15">
         <v>16</v>
@@ -2306,11 +2640,11 @@
       <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="28">
         <v>6</v>
       </c>
       <c r="F15">
-        <f t="shared" ref="F15" si="4">B15*E15</f>
+        <f t="shared" ref="F15" si="5">B15*E15</f>
         <v>96</v>
       </c>
       <c r="G15">
@@ -2321,10 +2655,13 @@
         <f>D15*E15</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="20" t="s">
-        <v>101</v>
+      <c r="I15" s="28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="18" t="s">
+        <v>88</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -2339,7 +2676,7 @@
         <v>3</v>
       </c>
       <c r="F16">
-        <f t="shared" ref="F16" si="5">B16*E16</f>
+        <f t="shared" ref="F16" si="6">B16*E16</f>
         <v>24</v>
       </c>
       <c r="G16">
@@ -2352,63 +2689,68 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="20"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ref="E20:F20" si="6">SUM(E2:E19)</f>
-        <v>202</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="6"/>
-        <v>514</v>
-      </c>
-      <c r="G20">
-        <f>SUM(G2:G19)</f>
-        <v>1876</v>
-      </c>
-      <c r="H20">
-        <f>SUM(H2:H19)</f>
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21">
-        <f>ROUNDUP(F20*1.3,0)</f>
-        <v>669</v>
-      </c>
-      <c r="G21">
-        <f>ROUNDUP(G20*1.3,0)</f>
-        <v>2439</v>
-      </c>
-      <c r="H21">
-        <f>ROUNDUP(H20*1.3,0)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="16.5">
-      <c r="L24" s="19"/>
+      <c r="A17" s="18"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="28">
+        <f>SUM(F2:F17)</f>
+        <v>362</v>
+      </c>
+      <c r="G18" s="28">
+        <f>SUM(G2:G17)</f>
+        <v>1444</v>
+      </c>
+      <c r="H18" s="38">
+        <f>SUM(H2:H17)</f>
+        <v>41.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="28">
+        <f>ROUNDUP(F18*1.3,0)</f>
+        <v>471</v>
+      </c>
+      <c r="G19" s="28">
+        <f>ROUNDUP(G18*1.3,0)</f>
+        <v>1878</v>
+      </c>
+      <c r="H19" s="28">
+        <f>ROUNDUP(H18*1.3,0)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="16.5">
+      <c r="L22" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F014613-D9AD-49C8-8029-E84AD574E5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BB7E76-7B6E-4524-8714-BA322824FC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
   <si>
     <t>Категория пользователей</t>
   </si>
@@ -277,9 +277,6 @@
     <t>Гео-сервис</t>
   </si>
   <si>
-    <t>1 instance = ~1 000 RPS</t>
-  </si>
-  <si>
     <t>OPS</t>
   </si>
   <si>
@@ -378,12 +375,6 @@
     <t>Сервис резерва</t>
   </si>
   <si>
-    <t>Сервис комманд</t>
-  </si>
-  <si>
-    <t>Адаптеры (POS/WMS/OMS)</t>
-  </si>
-  <si>
     <t>Распределенный кеш</t>
   </si>
   <si>
@@ -444,12 +435,6 @@
     <t>9-12</t>
   </si>
   <si>
-    <t>Worst-case Redis (hot SKU + burst)</t>
-  </si>
-  <si>
-    <t>Дополнительный burst 30% поверх нагрузки hot SKU</t>
-  </si>
-  <si>
     <t>Worst-case нагрузка (Read), RPS</t>
   </si>
   <si>
@@ -489,16 +474,119 @@
     <t>- брокеры (для 9–12 партиций)</t>
   </si>
   <si>
-    <t>Конфигурация принята исходя из требований отказоустойчивости, а не только из расчетной TPS-нагрузки</t>
-  </si>
-  <si>
-    <t>Количество брокеров определено исходя из 9–12 партиций и replication factor</t>
-  </si>
-  <si>
     <t>--</t>
   </si>
   <si>
     <t>PostgreSQL хранилища событий (конфигурация отказоустойчивости)</t>
+  </si>
+  <si>
+    <t>Сервис команд</t>
+  </si>
+  <si>
+    <t>Worst-case Redis (hot SKU + burst),
+Дополнительный burst 30% поверх нагрузки hot SKU</t>
+  </si>
+  <si>
+    <t>API Gateway</t>
+  </si>
+  <si>
+    <t>Load Ballancer</t>
+  </si>
+  <si>
+    <t>Сервис сверки</t>
+  </si>
+  <si>
+    <t>1 инстанс = 20 000 RPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = 200 EPS</t>
+  </si>
+  <si>
+    <t>Админ-сервис</t>
+  </si>
+  <si>
+    <t>1 инстанс = 1 000 EPS</t>
+  </si>
+  <si>
+    <t>Адаптер ERP</t>
+  </si>
+  <si>
+    <t>Адаптер службы доставки</t>
+  </si>
+  <si>
+    <t>1 инстанс = 100 TPS</t>
+  </si>
+  <si>
+    <t>Сервис прогрева кэша</t>
+  </si>
+  <si>
+    <t>1 инстанс = 2 000 OPS</t>
+  </si>
+  <si>
+    <t>Сервис синхронизации кеша</t>
+  </si>
+  <si>
+    <t>Клиент Лояльности</t>
+  </si>
+  <si>
+    <t>1 инстанс = ~2 000 RPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = ~5 000 RPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = ~1 000 RPS</t>
+  </si>
+  <si>
+    <t>Метаданные, справочники</t>
+  </si>
+  <si>
+    <t>Хранилище временных рядов</t>
+  </si>
+  <si>
+    <t>samples/s</t>
+  </si>
+  <si>
+    <t>1 узел = ~50 000 samples/s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кэш  лояльности </t>
+  </si>
+  <si>
+    <t>1 инстанс = ~8 000 OPS</t>
+  </si>
+  <si>
+    <t>Захват изменений (CDC)</t>
+  </si>
+  <si>
+    <t>1 инстанс = ~2 000 EPS</t>
+  </si>
+  <si>
+    <t>Менеджер блокировок</t>
+  </si>
+  <si>
+    <t>1 инстанс = ~3 000 RPS</t>
+  </si>
+  <si>
+    <t>Управление секретами</t>
+  </si>
+  <si>
+    <t>Реестр схем</t>
+  </si>
+  <si>
+    <t>Адаптеры (POS/WMS/OMS/PPE)</t>
+  </si>
+  <si>
+    <t>Сервис агрегации метрик</t>
+  </si>
+  <si>
+    <t>Система логирования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Система мониторинга и трассировки </t>
+  </si>
+  <si>
+    <t>Оповещение</t>
   </si>
 </sst>
 </file>
@@ -514,7 +602,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,22 +652,23 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -588,27 +677,53 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -619,76 +734,86 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1019,186 +1144,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>0.1</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="12">
         <v>80000</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="13">
         <f>C2/C$6</f>
         <v>0.95408467501490757</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="12">
         <f>C2*B2</f>
         <v>8000</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="12">
         <v>400000</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="13">
         <f>F2/F$6</f>
         <v>0.95923261390887293</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="12">
         <f>F2*B2</f>
         <v>40000</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12">
         <v>750</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="13">
         <f t="shared" ref="D3:D5" si="0">C3/C$6</f>
         <v>8.9445438282647581E-3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="12">
         <f t="shared" ref="E3:E4" si="1">C3*B3</f>
         <v>1500</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="12">
         <v>4000</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="13">
         <f t="shared" ref="G3:G5" si="2">F3/F$6</f>
         <v>9.5923261390887284E-3</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="12">
         <f t="shared" ref="H3:H4" si="3">F3*B3</f>
         <v>8000</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A4" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <v>0.2</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="12">
         <v>2500</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="13">
         <f t="shared" si="0"/>
         <v>2.9815146094215862E-2</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="12">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="12">
         <v>10000</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="13">
         <f t="shared" si="2"/>
         <v>2.3980815347721823E-2</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="12">
         <f t="shared" si="3"/>
         <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
         <v>6</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="12">
         <v>600</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="13">
         <f t="shared" si="0"/>
         <v>7.1556350626118068E-3</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="12">
         <f>C5/B5</f>
         <v>100</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="12">
         <v>3000</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="13">
         <f t="shared" si="2"/>
         <v>7.1942446043165471E-3</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="12">
         <f>F5/B5</f>
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1">
-      <c r="A6" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="2">
+      <c r="B6" s="4"/>
+      <c r="C6" s="12">
         <f>SUM(C2:C5)</f>
         <v>83850</v>
       </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="12">
         <f>SUM(E2:E4)</f>
         <v>10000</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="12">
         <f>SUM(F2:F5)</f>
         <v>417000</v>
       </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="12">
         <f>SUM(H2:H4)</f>
         <v>50000</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="28">
+      <c r="A7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="4">
         <v>0.1</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="29">
+      <c r="A8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="14">
         <f>E6*B7</f>
         <v>1000</v>
       </c>
-      <c r="H8" s="29">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="14">
         <f>H6*B7</f>
         <v>5000</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="E16" s="3"/>
+      <c r="E16" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1224,7 +1362,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -1235,167 +1373,167 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="8">
         <v>10000</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="8">
         <v>50000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>0.85</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>0.85</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="8">
         <f>B2*B3</f>
         <v>8500</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="8">
         <f>C2*C3</f>
         <v>42500</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="4">
         <v>1.75</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="8">
         <f>B4*B5</f>
         <v>14875</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="8">
         <f>C4*C5</f>
         <v>85000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="32">
+      <c r="A7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="8">
         <f>B6*1.3</f>
         <v>19337.5</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="8">
         <f>C6*1.3</f>
         <v>110500</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>100</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="8">
         <f>'Нагрузка по категориям'!E8</f>
         <v>1000</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="8">
         <f>'Нагрузка по категориям'!H8</f>
         <v>5000</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="28">
+      <c r="A10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="4">
         <v>0.8</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="4">
         <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" t="s">
+      <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>40</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>200</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="11">
         <f>B6*(B11+B12)*B13/1024^2</f>
         <v>3.7450790405273442</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="11">
         <f>C6*(C11+C12)*C13/1024^2</f>
         <v>21.40045166015625</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="11">
         <f>(B8+B9*B10)*(B11+B12)*B13/1024^2</f>
         <v>0.22659301757812503</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="11">
         <f>(C8+C9*C10)*(C11+C12)*C13/1024^2</f>
         <v>1.132965087890625</v>
       </c>
@@ -1417,7 +1555,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -1428,85 +1566,85 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="8">
         <f>'Нагрузка по категориям'!E8</f>
         <v>1000</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="8">
         <f>'Нагрузка по категориям'!H8</f>
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="8">
         <v>500</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="8">
         <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="10">
         <f>B2*B3/1024^2</f>
         <v>0.476837158203125</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="10">
         <f>C2*C3/1024^2</f>
         <v>2.384185791015625</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="10">
         <f>B4*24*3600/1024</f>
         <v>40.233135223388672</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="10">
         <f>C4*24*3600/1024</f>
         <v>201.16567611694336</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="32">
+      <c r="A6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="8">
         <v>1000</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="8">
         <v>5000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="4">
         <v>5</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30">
-      <c r="A8" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="28">
+      <c r="A8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="4">
         <v>1000</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="4">
         <v>5000</v>
       </c>
     </row>
@@ -1527,7 +1665,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -1538,121 +1676,121 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="A2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="8">
         <f>'Нагрузка по категориям'!E8</f>
         <v>1000</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="8">
         <f>'Нагрузка по категориям'!H8</f>
         <v>5000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>3</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="8">
         <f>B2*B3</f>
         <v>3000</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="8">
         <f>C2*C3</f>
         <v>15000</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>1.4</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>1.4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <f>B4*B5/1000*B6</f>
         <v>4.1999999999999993</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <f>C4*C5/1000*C6</f>
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="A9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="8">
         <f>B2*B8</f>
         <v>4000</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="8">
         <f>C2*C8</f>
         <v>20000</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10">
+      <c r="A10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="4">
         <v>1.3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="A11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="8">
         <f>B9*B10</f>
         <v>5200</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="8">
         <f>C9*C10</f>
         <v>30000</v>
       </c>
@@ -1675,9 +1813,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="B1" s="4"/>
       <c r="C1" s="7" t="s">
         <v>18</v>
       </c>
@@ -1686,118 +1825,123 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="4">
+      <c r="B2" s="4"/>
+      <c r="C2" s="8">
         <v>100</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="8">
         <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>0.5</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="8">
         <f>C2*$B3</f>
         <v>50</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="8">
         <f>D2*$B3</f>
         <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8">
         <f>C2*$B4</f>
         <v>200</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="8">
         <f>D2*$B4</f>
         <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="21">
+      <c r="B5" s="4"/>
+      <c r="C5" s="25">
         <v>3</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="25"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>5</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="8">
         <f>C2*$B6*$C5</f>
         <v>1500</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="8">
         <f>D2*$B6*$C5</f>
         <v>7500</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7">
+      <c r="A7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4">
         <v>1.75</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="A8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="8">
         <f>C6*C7</f>
         <v>2625</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="8">
         <f>D6*D7</f>
         <v>15000</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="A9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="21">
+      <c r="B9" s="4"/>
+      <c r="C9" s="25">
         <v>400</v>
       </c>
-      <c r="D9" s="21"/>
+      <c r="D9" s="25"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="4">
         <v>15</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="10">
         <f>C2*$C9*$B10*60/1024^2</f>
         <v>34.332275390625</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="10">
         <f>D2*$C9*$B10*60/1024^2</f>
         <v>171.661376953125</v>
       </c>
@@ -1824,9 +1968,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="B1" s="4"/>
       <c r="C1" s="7" t="s">
         <v>18</v>
       </c>
@@ -1835,113 +1980,119 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4">
+      <c r="B2" s="9"/>
+      <c r="C2" s="8">
         <v>10000</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="8">
         <v>50000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="22">
+      <c r="B3" s="4"/>
+      <c r="C3" s="26">
         <v>0.1</v>
       </c>
-      <c r="D3" s="23"/>
+      <c r="D3" s="27"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="4">
+      <c r="B4" s="4"/>
+      <c r="C4" s="8">
         <f>C2*$C3</f>
         <v>1000</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="8">
         <f>D2*$C3</f>
         <v>5000</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="21">
+      <c r="B5" s="4"/>
+      <c r="C5" s="25">
         <v>200</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="25"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="4">
+      <c r="B6" s="4"/>
+      <c r="C6" s="8">
         <f>C4*$C5/1000</f>
         <v>200</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="8">
         <f>D4*$C5/1000</f>
         <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="4">
+        <v>4</v>
+      </c>
+      <c r="C7" s="8">
         <f>C4*$B7</f>
         <v>4000</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="8">
         <f>D4*$B7</f>
         <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="A8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>20</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="8">
         <f>C4*$B8</f>
         <v>20000</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="8">
         <f>D4*$B8</f>
         <v>100000</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9">
+      <c r="A9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4">
         <v>1.75</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="4">
+      <c r="A10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="8">
         <f>C8*C9</f>
         <v>35000</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="8">
         <f>D8*D9</f>
         <v>200000</v>
       </c>
@@ -1958,303 +2109,795 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEACBF24-690E-480A-A550-EDA8CDE0ADBA}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="44.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30">
-      <c r="B1" s="24" t="s">
+    <row r="1" spans="1:9" ht="30">
+      <c r="A1" s="4"/>
+      <c r="B1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="E1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="16"/>
+      <c r="H1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="17">
+        <v>50000</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="17">
+        <v>2500</v>
+      </c>
+      <c r="F2" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="14">
-        <v>50000</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="14">
-        <v>2500</v>
-      </c>
-      <c r="F2" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="16">
+      <c r="H2" s="19">
         <f>B2/E2*F2</f>
         <v>30</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="17">
         <f>H2</f>
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="30">
-      <c r="A3" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="19">
+    <row r="3" spans="1:9" ht="30">
+      <c r="A3" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="17">
         <v>85000</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="19">
+      <c r="C3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="17">
         <v>9000</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="18">
         <v>1.5</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="16">
+      <c r="G3" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="19">
         <f>(B3+B4)/E3*F3</f>
         <v>15.083333333333332</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="21">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="30"/>
-      <c r="B4" s="14">
+    <row r="4" spans="1:9">
+      <c r="A4" s="20"/>
+      <c r="B4" s="17">
         <v>5500</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="30">
-      <c r="A5" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" ht="30">
+      <c r="A5" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="14">
         <f>B3*1.3</f>
         <v>110500</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="19">
+      <c r="C5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="17">
         <v>9000</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="18">
         <v>1.5</v>
       </c>
-      <c r="G5" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="37">
+      <c r="G5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="19">
         <f>(B5+B6)/E5*F5</f>
         <v>19.25</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="21">
         <v>20</v>
       </c>
-      <c r="J5" s="35" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="14">
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="17">
         <v>5000</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="C6" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="17">
         <v>800</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="18">
         <v>1.3</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="16">
+      <c r="G6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="19">
         <f>B6/E6*F6</f>
         <v>8.125</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="30"/>
-      <c r="B7" s="14">
+      <c r="I6" s="21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="20"/>
+      <c r="B7" s="17">
         <v>3</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
+      <c r="C7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="17">
         <v>5000</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="14">
+      <c r="C8" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="17">
         <v>500</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="18">
         <v>1.2</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="16">
+      <c r="G8" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="19">
         <f>B8/E8*F8</f>
         <v>12</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
+    <row r="9" spans="1:9">
+      <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="17">
         <v>500</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="14">
+      <c r="C9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="17">
         <v>200</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="18">
         <v>1.5</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="16">
+      <c r="G9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="19">
         <f>B9/E9*F9</f>
         <v>3.75</v>
       </c>
-      <c r="I9" s="34">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="25" t="s">
+      <c r="I9" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="17">
         <v>5000</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="14">
+      <c r="C10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="17">
         <v>1000</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="18">
         <v>1.3</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="16">
+      <c r="G10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="19">
         <f>B10/E10*F10</f>
         <v>6.5</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="22">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="25"/>
-      <c r="B11" s="14">
+    <row r="11" spans="1:9">
+      <c r="A11" s="29"/>
+      <c r="B11" s="17">
         <v>20</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="26"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="28" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="28" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="28" t="s">
-        <v>108</v>
+      <c r="C11" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="17">
+        <v>50000</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="17">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="19">
+        <f>B12/E12*F12</f>
+        <v>15</v>
+      </c>
+      <c r="I12" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="17">
+        <v>50000</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="17">
+        <v>20000</v>
+      </c>
+      <c r="F13" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="19">
+        <f>B13/E13*F13</f>
+        <v>3.25</v>
+      </c>
+      <c r="I13" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="17">
+        <v>250</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="17">
+        <v>200</v>
+      </c>
+      <c r="F14" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="19">
+        <f>B14/E14*F14</f>
+        <v>1.875</v>
+      </c>
+      <c r="I14" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="17">
+        <v>500</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="19">
+        <f>B15/E15*F15</f>
+        <v>0.75</v>
+      </c>
+      <c r="I15" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="17">
+        <v>250</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" s="17">
+        <v>100</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="19">
+        <f>B16/E16*F16</f>
+        <v>3.75</v>
+      </c>
+      <c r="I16" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="17">
+        <v>250</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" s="17">
+        <v>100</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="19">
+        <f>B17/E17*F17</f>
+        <v>3.75</v>
+      </c>
+      <c r="I17" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="17">
+        <v>10000</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" s="17">
+        <v>2000</v>
+      </c>
+      <c r="F18" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="19">
+        <f>B18/E18*F18</f>
+        <v>7.5</v>
+      </c>
+      <c r="I18" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="17">
+        <v>5000</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="19">
+        <f>B19/E19*F19</f>
+        <v>7.5</v>
+      </c>
+      <c r="I19" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="17">
+        <v>10000</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E20" s="17">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="19">
+        <f>B20/E20*F20</f>
+        <v>7.5</v>
+      </c>
+      <c r="I20" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="17">
+        <v>1000</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="17">
+        <v>2000</v>
+      </c>
+      <c r="F21" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="19">
+        <f>B21/E21*F21</f>
+        <v>0.75</v>
+      </c>
+      <c r="I21" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" s="17">
+        <v>100000</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="17">
+        <v>50000</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="19">
+        <f>B22/E22*F22</f>
+        <v>3</v>
+      </c>
+      <c r="I22" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="17">
+        <v>10000</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" s="17">
+        <v>8000</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="19">
+        <f>B23/E23*F23</f>
+        <v>1.875</v>
+      </c>
+      <c r="I23" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="17">
+        <v>5000</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="17">
+        <v>2000</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" s="19">
+        <f>B24/E24*F24</f>
+        <v>3.75</v>
+      </c>
+      <c r="I24" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="17">
+        <v>7500</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3000</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" s="19">
+        <f>B25/E25*F25</f>
+        <v>3.75</v>
+      </c>
+      <c r="I25" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="23"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="23"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="23"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="23"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="23"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2263,6 +2906,7 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="C11:D11"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2270,7 +2914,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F55A25-67AE-4582-B6E5-DF4CB5C7DF4D}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -2281,478 +2925,1079 @@
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="99.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="126.7109375" customWidth="1"/>
+    <col min="9" max="13" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2" s="28">
+      <c r="B2" s="4">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4">
         <v>0.05</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <f>'Расчет параметров'!I2</f>
         <v>30</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <f>B2*E2</f>
         <v>60</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="4">
         <f t="shared" ref="G2:G7" si="0">C2*E2</f>
         <v>120</v>
       </c>
-      <c r="H2" s="28">
-        <f t="shared" ref="H2:H14" si="1">D2*E2</f>
+      <c r="H2" s="4">
+        <f t="shared" ref="H2:H13" si="1">D2*E2</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
+    <row r="3" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="4">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4">
         <v>8</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="4">
         <v>0.1</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <f>'Расчет параметров'!I9</f>
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <f t="shared" ref="F3:F10" si="2">B3*E3</f>
         <v>16</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="4">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" s="28">
+    <row r="4" spans="1:8">
+      <c r="A4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4">
         <v>0.05</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>6</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="4">
         <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="28">
+      <c r="B5" s="4">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
         <v>0.1</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <f>'Расчет параметров'!I8</f>
         <v>12</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="4">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="4">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="4">
         <f t="shared" si="1"/>
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6" s="28">
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4">
         <v>0.05</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <f>'Расчет параметров'!I10</f>
         <v>7</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="4">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="4">
         <f t="shared" si="1"/>
         <v>0.35000000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7">
+    <row r="7" spans="1:8">
+      <c r="A7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" s="28">
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
         <v>0.05</v>
       </c>
-      <c r="E7">
-        <v>12</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="4">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="H7" s="28">
+        <v>32</v>
+      </c>
+      <c r="H7" s="4">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="28"/>
-      <c r="H8" s="28"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="4">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4">
         <v>32</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="4">
         <v>0.2</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>8</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="4">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="4">
         <f>C9*E9</f>
         <v>256</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="4">
         <f t="shared" si="1"/>
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10">
+    <row r="10" spans="1:8">
+      <c r="A10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="4">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4">
         <v>64</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="4">
         <v>0.2</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>8</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="4">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="4">
         <f>C10*E10</f>
         <v>512</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="4">
         <f t="shared" si="1"/>
         <v>1.6</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="H11" s="28"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12">
+    <row r="11" spans="1:8">
+      <c r="A11" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="33"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="4">
         <v>16</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>64</v>
       </c>
-      <c r="D12" s="28">
-        <v>2</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="4">
         <f t="shared" ref="F12" si="3">B12*E12</f>
         <v>16</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="4">
         <f>C12*E12</f>
         <v>64</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="4">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="I12" s="28" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13">
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="4">
         <v>8</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>32</v>
       </c>
-      <c r="D13" s="28">
-        <v>2</v>
-      </c>
-      <c r="E13">
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
         <v>3</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="4">
         <f t="shared" ref="F13" si="4">B13*E13</f>
         <v>24</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="4">
         <f>C13*E13</f>
         <v>96</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="4">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15">
+    <row r="14" spans="1:8">
+      <c r="A14" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="4">
         <v>16</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>32</v>
       </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15" s="28">
+      <c r="D15" s="4">
+        <v>4</v>
+      </c>
+      <c r="E15" s="4">
         <v>6</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="4">
         <f t="shared" ref="F15" si="5">B15*E15</f>
         <v>96</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="4">
         <f>C15*E15</f>
         <v>192</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="4">
         <f>D15*E15</f>
         <v>24</v>
       </c>
-      <c r="I15" s="28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16">
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="4">
         <v>8</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="4">
         <v>16</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="4">
         <v>0.5</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>3</v>
       </c>
-      <c r="F16">
-        <f t="shared" ref="F16" si="6">B16*E16</f>
+      <c r="F16" s="4">
+        <f t="shared" ref="F16:F17" si="6">B16*E16</f>
         <v>24</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="4">
         <f>C16*E16</f>
         <v>48</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="4">
         <f>D16*E16</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="18"/>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
+    <row r="17" spans="1:8">
+      <c r="A17" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="4">
+        <v>4</v>
+      </c>
+      <c r="C17" s="4">
+        <v>8</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="9">
+        <v>15</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="G17" s="4">
+        <f>C17*E17</f>
+        <v>120</v>
+      </c>
+      <c r="H17" s="4">
+        <f>D17*E17</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E18" s="9">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" ref="F18" si="7">B18*E18</f>
+        <v>8</v>
+      </c>
+      <c r="G18" s="4">
+        <f>C18*E18</f>
+        <v>16</v>
+      </c>
+      <c r="H18" s="4">
+        <f>D18*E18</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4">
+        <f t="shared" ref="F19:F22" si="8">B19*E19</f>
+        <v>4</v>
+      </c>
+      <c r="G19" s="4">
+        <f>C19*E19</f>
+        <v>8</v>
+      </c>
+      <c r="H19" s="4">
+        <f>D19*E19</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="G20" s="4">
+        <f>C20*E20</f>
+        <v>4</v>
+      </c>
+      <c r="H20" s="4">
+        <f>D20*E20</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4">
+        <v>4</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E21" s="9">
+        <v>4</v>
+      </c>
+      <c r="F21" s="4">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="G21" s="4">
+        <f>C21*E21</f>
+        <v>16</v>
+      </c>
+      <c r="H21" s="4">
+        <f>D21*E21</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2</v>
+      </c>
+      <c r="C22" s="4">
+        <v>4</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E22" s="9">
+        <v>4</v>
+      </c>
+      <c r="F22" s="4">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="G22" s="4">
+        <f>C22*E22</f>
+        <v>16</v>
+      </c>
+      <c r="H22" s="4">
+        <f>D22*E22</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4">
+        <v>4</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E23" s="9">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4">
+        <f t="shared" ref="F23" si="9">B23*E23</f>
+        <v>16</v>
+      </c>
+      <c r="G23" s="4">
+        <f>C23*E23</f>
+        <v>32</v>
+      </c>
+      <c r="H23" s="4">
+        <f>D23*E23</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
+        <v>4</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E24" s="9">
+        <v>8</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" ref="F24" si="10">B24*E24</f>
+        <v>16</v>
+      </c>
+      <c r="G24" s="4">
+        <f>C24*E24</f>
+        <v>32</v>
+      </c>
+      <c r="H24" s="4">
+        <f>D24*E24</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
+        <v>4</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E25" s="9">
+        <v>8</v>
+      </c>
+      <c r="F25" s="4">
+        <f t="shared" ref="F25:F36" si="11">B25*E25</f>
+        <v>16</v>
+      </c>
+      <c r="G25" s="4">
+        <f>C25*E25</f>
+        <v>32</v>
+      </c>
+      <c r="H25" s="4">
+        <f>D25*E25</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="4">
+        <v>4</v>
+      </c>
+      <c r="C26" s="4">
+        <v>8</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E26" s="9">
+        <v>2</v>
+      </c>
+      <c r="F26" s="4">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G26" s="4">
+        <f>C26*E26</f>
+        <v>16</v>
+      </c>
+      <c r="H26" s="4">
+        <f>D26*E26</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="4">
+        <v>4</v>
+      </c>
+      <c r="C27" s="4">
+        <v>8</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="9">
+        <v>3</v>
+      </c>
+      <c r="F27" s="4">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="G27" s="4">
+        <f>C27*E27</f>
+        <v>24</v>
+      </c>
+      <c r="H27" s="4">
+        <f>D27*E27</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4">
+        <v>8</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="G28" s="4">
+        <f>C28*E28</f>
+        <v>16</v>
+      </c>
+      <c r="H28" s="4">
+        <f>D28*E28</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="G29" s="4">
+        <f>C29*E29</f>
+        <v>4</v>
+      </c>
+      <c r="H29" s="4">
+        <f>D29*E29</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4">
+        <v>4</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E30" s="9">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G30" s="4">
+        <f>C30*E30</f>
+        <v>16</v>
+      </c>
+      <c r="H30" s="4">
+        <f>D30*E30</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4">
+        <v>4</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E31" s="9">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="G31" s="4">
+        <f>C31*E31</f>
+        <v>16</v>
+      </c>
+      <c r="H31" s="4">
+        <f>D31*E31</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4">
+        <v>4</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E32" s="4">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="G32" s="4">
+        <f>C32*E32</f>
+        <v>12</v>
+      </c>
+      <c r="H32" s="4">
+        <f>D32*E32</f>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" s="4">
+        <v>4</v>
+      </c>
+      <c r="C33" s="4">
+        <v>8</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4">
+        <v>3</v>
+      </c>
+      <c r="F33" s="4">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="G33" s="4">
+        <f>C33*E33</f>
+        <v>24</v>
+      </c>
+      <c r="H33" s="4">
+        <f>D33*E33</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" s="4">
+        <v>4</v>
+      </c>
+      <c r="C34" s="4">
+        <v>16</v>
+      </c>
+      <c r="D34" s="4">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="G34" s="4">
+        <f>C34*E34</f>
+        <v>48</v>
+      </c>
+      <c r="H34" s="4">
+        <f>D34*E34</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="4">
+        <v>4</v>
+      </c>
+      <c r="C35" s="4">
+        <v>8</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4">
+        <v>3</v>
+      </c>
+      <c r="F35" s="4">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="G35" s="4">
+        <f>C35*E35</f>
+        <v>24</v>
+      </c>
+      <c r="H35" s="4">
+        <f>D35*E35</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B36" s="4">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4">
+        <v>2</v>
+      </c>
+      <c r="D36" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E36" s="4">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="G36" s="4">
+        <f>C36*E36</f>
+        <v>4</v>
+      </c>
+      <c r="H36" s="4">
+        <f>D36*E36</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F38" s="4">
+        <f>SUM(F2:F37)</f>
+        <v>596</v>
+      </c>
+      <c r="G38" s="4">
+        <f>SUM(G2:G37)</f>
+        <v>1932</v>
+      </c>
+      <c r="H38" s="6">
+        <f>ROUNDUP(SUM(H2:H37),0)</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="28">
-        <f>SUM(F2:F17)</f>
-        <v>362</v>
-      </c>
-      <c r="G18" s="28">
-        <f>SUM(G2:G17)</f>
-        <v>1444</v>
-      </c>
-      <c r="H18" s="38">
-        <f>SUM(H2:H17)</f>
-        <v>41.05</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="28">
-        <f>ROUNDUP(F18*1.3,0)</f>
-        <v>471</v>
-      </c>
-      <c r="G19" s="28">
-        <f>ROUNDUP(G18*1.3,0)</f>
-        <v>1878</v>
-      </c>
-      <c r="H19" s="28">
-        <f>ROUNDUP(H18*1.3,0)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="16.5">
-      <c r="L22" s="17"/>
+      <c r="B39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="4">
+        <f>ROUNDUP(F38*1.3,0)</f>
+        <v>775</v>
+      </c>
+      <c r="G39" s="4">
+        <f>ROUNDUP(G38*1.3,0)</f>
+        <v>2512</v>
+      </c>
+      <c r="H39" s="4">
+        <f>ROUNDUP(H38*1.3,0)</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="16.5">
+      <c r="L42" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BB7E76-7B6E-4524-8714-BA322824FC17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083FBC0B-766D-427B-A564-B9D39C5EB32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <sheet name="Гео-поиск" sheetId="6" r:id="rId6"/>
     <sheet name="Расчет параметров" sheetId="7" r:id="rId7"/>
     <sheet name="Расчет ресурсов" sheetId="8" r:id="rId8"/>
+    <sheet name="Лист1" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="164">
   <si>
     <t>Категория пользователей</t>
   </si>
@@ -587,6 +588,51 @@
   </si>
   <si>
     <t>Оповещение</t>
+  </si>
+  <si>
+    <t>Гео-индекс, координаты</t>
+  </si>
+  <si>
+    <t>БД резервирования</t>
+  </si>
+  <si>
+    <t>БД реестра схем</t>
+  </si>
+  <si>
+    <t>БД конфликтов</t>
+  </si>
+  <si>
+    <t>БД прогрева кэша</t>
+  </si>
+  <si>
+    <t>Кэш лояльности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS </t>
+  </si>
+  <si>
+    <t>1 инстанс = 2 500 RPS</t>
+  </si>
+  <si>
+    <t>- запись (primary)</t>
+  </si>
+  <si>
+    <t>- чтение (replica)</t>
+  </si>
+  <si>
+    <t>1 инстанс = 1 500 TPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = 500 TPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = 1 000 OPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = 500 OPS</t>
+  </si>
+  <si>
+    <t>1 инстанс = 8 000 RPS</t>
   </si>
 </sst>
 </file>
@@ -734,7 +780,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -778,6 +824,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -796,24 +860,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1148,16 +1202,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="4"/>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
@@ -1873,10 +1927,10 @@
         <v>34</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="25">
+      <c r="C5" s="31">
         <v>3</v>
       </c>
-      <c r="D5" s="25"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -1925,10 +1979,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="25">
+      <c r="C9" s="31">
         <v>400</v>
       </c>
-      <c r="D9" s="25"/>
+      <c r="D9" s="31"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
@@ -1996,10 +2050,10 @@
         <v>39</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="26">
+      <c r="C3" s="32">
         <v>0.1</v>
       </c>
-      <c r="D3" s="27"/>
+      <c r="D3" s="33"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
@@ -2020,10 +2074,10 @@
         <v>37</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="25">
+      <c r="C5" s="31">
         <v>200</v>
       </c>
-      <c r="D5" s="25"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -2109,7 +2163,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEACBF24-690E-480A-A550-EDA8CDE0ADBA}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
@@ -2126,10 +2180,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30">
       <c r="A1" s="4"/>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="28"/>
+      <c r="C1" s="34"/>
       <c r="D1" s="9" t="s">
         <v>43</v>
       </c>
@@ -2356,7 +2410,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="35" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="17">
@@ -2386,14 +2440,14 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="29"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="17">
         <v>20</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="30"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
@@ -2423,7 +2477,7 @@
         <v>60</v>
       </c>
       <c r="H12" s="19">
-        <f>B12/E12*F12</f>
+        <f t="shared" ref="H12:H30" si="0">B12/E12*F12</f>
         <v>15</v>
       </c>
       <c r="I12" s="9">
@@ -2453,7 +2507,7 @@
         <v>60</v>
       </c>
       <c r="H13" s="19">
-        <f>B13/E13*F13</f>
+        <f t="shared" si="0"/>
         <v>3.25</v>
       </c>
       <c r="I13" s="9">
@@ -2483,7 +2537,7 @@
         <v>60</v>
       </c>
       <c r="H14" s="19">
-        <f>B14/E14*F14</f>
+        <f t="shared" si="0"/>
         <v>1.875</v>
       </c>
       <c r="I14" s="9">
@@ -2513,7 +2567,7 @@
         <v>60</v>
       </c>
       <c r="H15" s="19">
-        <f>B15/E15*F15</f>
+        <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
       <c r="I15" s="9">
@@ -2543,7 +2597,7 @@
         <v>60</v>
       </c>
       <c r="H16" s="19">
-        <f>B16/E16*F16</f>
+        <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
       <c r="I16" s="9">
@@ -2573,7 +2627,7 @@
         <v>60</v>
       </c>
       <c r="H17" s="19">
-        <f>B17/E17*F17</f>
+        <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
       <c r="I17" s="9">
@@ -2603,7 +2657,7 @@
         <v>60</v>
       </c>
       <c r="H18" s="19">
-        <f>B18/E18*F18</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="I18" s="9">
@@ -2633,7 +2687,7 @@
         <v>60</v>
       </c>
       <c r="H19" s="19">
-        <f>B19/E19*F19</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="I19" s="9">
@@ -2663,7 +2717,7 @@
         <v>60</v>
       </c>
       <c r="H20" s="19">
-        <f>B20/E20*F20</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
       <c r="I20" s="9">
@@ -2693,7 +2747,7 @@
         <v>60</v>
       </c>
       <c r="H21" s="19">
-        <f>B21/E21*F21</f>
+        <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
       <c r="I21" s="9">
@@ -2723,7 +2777,7 @@
         <v>61</v>
       </c>
       <c r="H22" s="19">
-        <f>B22/E22*F22</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I22" s="9">
@@ -2753,7 +2807,7 @@
         <v>60</v>
       </c>
       <c r="H23" s="19">
-        <f>B23/E23*F23</f>
+        <f t="shared" si="0"/>
         <v>1.875</v>
       </c>
       <c r="I23" s="9">
@@ -2783,7 +2837,7 @@
         <v>60</v>
       </c>
       <c r="H24" s="19">
-        <f>B24/E24*F24</f>
+        <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
       <c r="I24" s="9">
@@ -2813,7 +2867,7 @@
         <v>60</v>
       </c>
       <c r="H25" s="19">
-        <f>B25/E25*F25</f>
+        <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
       <c r="I25" s="9">
@@ -2821,18 +2875,39 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="23"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="9"/>
+      <c r="A26" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="17">
+        <v>5000</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="17">
+        <v>2500</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="19">
+        <f t="shared" si="0"/>
+        <v>2.6</v>
+      </c>
+      <c r="I26" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="23"/>
+      <c r="A27" s="23" t="s">
+        <v>150</v>
+      </c>
       <c r="B27" s="17"/>
       <c r="C27" s="24"/>
       <c r="D27" s="9"/>
@@ -2843,60 +2918,207 @@
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="23"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="9"/>
+      <c r="A28" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="17">
+        <v>750</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="17">
+        <v>1500</v>
+      </c>
+      <c r="F28" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="19">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="I28" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="23"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="9"/>
+      <c r="A29" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="17">
+        <v>1000</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="17">
+        <v>500</v>
+      </c>
+      <c r="F29" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" s="19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I29" s="9">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="23"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="9"/>
+      <c r="A30" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="17">
+        <v>500</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="17">
+        <v>1000</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" s="19">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="I30" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" t="s">
+      <c r="A31" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" s="17">
+        <v>250</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="17">
+        <v>200</v>
+      </c>
+      <c r="F31" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H31" s="19">
+        <f t="shared" ref="H31:H33" si="1">B31/E31*F31</f>
+        <v>1.875</v>
+      </c>
+      <c r="I31" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" s="17">
+        <v>1000</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="17">
+        <v>500</v>
+      </c>
+      <c r="F32" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" s="19">
+        <f t="shared" si="1"/>
+        <v>2.6</v>
+      </c>
+      <c r="I32" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" s="17">
+        <v>10000</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E33" s="17">
+        <v>8000</v>
+      </c>
+      <c r="F33" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H33" s="19">
+        <f t="shared" si="1"/>
+        <v>1.875</v>
+      </c>
+      <c r="I33" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" t="s">
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2914,7 +3136,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F55A25-67AE-4582-B6E5-DF4CB5C7DF4D}">
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -3203,16 +3425,16 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
@@ -3273,16 +3495,16 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="30"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
@@ -3305,11 +3527,11 @@
         <v>96</v>
       </c>
       <c r="G15" s="4">
-        <f>C15*E15</f>
+        <f t="shared" ref="G15:G40" si="6">C15*E15</f>
         <v>192</v>
       </c>
       <c r="H15" s="4">
-        <f>D15*E15</f>
+        <f t="shared" ref="H15:H40" si="7">D15*E15</f>
         <v>24</v>
       </c>
     </row>
@@ -3330,15 +3552,15 @@
         <v>3</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" ref="F16:F17" si="6">B16*E16</f>
+        <f t="shared" ref="F16:F17" si="8">B16*E16</f>
         <v>24</v>
       </c>
       <c r="G16" s="4">
-        <f>C16*E16</f>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="H16" s="4">
-        <f>D16*E16</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
     </row>
@@ -3359,15 +3581,15 @@
         <v>15</v>
       </c>
       <c r="F17" s="4">
+        <f t="shared" si="8"/>
+        <v>60</v>
+      </c>
+      <c r="G17" s="4">
         <f t="shared" si="6"/>
-        <v>60</v>
-      </c>
-      <c r="G17" s="4">
-        <f>C17*E17</f>
         <v>120</v>
       </c>
       <c r="H17" s="4">
-        <f>D17*E17</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -3388,15 +3610,15 @@
         <v>4</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" ref="F18" si="7">B18*E18</f>
+        <f t="shared" ref="F18" si="9">B18*E18</f>
         <v>8</v>
       </c>
       <c r="G18" s="4">
-        <f>C18*E18</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H18" s="4">
-        <f>D18*E18</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3417,15 +3639,15 @@
         <v>2</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" ref="F19:F22" si="8">B19*E19</f>
+        <f t="shared" ref="F19:F22" si="10">B19*E19</f>
         <v>4</v>
       </c>
       <c r="G19" s="4">
-        <f>C19*E19</f>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="H19" s="4">
-        <f>D19*E19</f>
+        <f t="shared" si="7"/>
         <v>0.1</v>
       </c>
     </row>
@@ -3446,15 +3668,15 @@
         <v>2</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="G20" s="4">
-        <f>C20*E20</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H20" s="4">
-        <f>D20*E20</f>
+        <f t="shared" si="7"/>
         <v>0.1</v>
       </c>
     </row>
@@ -3475,15 +3697,15 @@
         <v>4</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="G21" s="4">
-        <f>C21*E21</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H21" s="4">
-        <f>D21*E21</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3504,15 +3726,15 @@
         <v>4</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="G22" s="4">
-        <f>C22*E22</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H22" s="4">
-        <f>D22*E22</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3533,15 +3755,15 @@
         <v>8</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" ref="F23" si="9">B23*E23</f>
+        <f t="shared" ref="F23" si="11">B23*E23</f>
         <v>16</v>
       </c>
       <c r="G23" s="4">
-        <f>C23*E23</f>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="H23" s="4">
-        <f>D23*E23</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
     </row>
@@ -3562,15 +3784,15 @@
         <v>8</v>
       </c>
       <c r="F24" s="4">
-        <f t="shared" ref="F24" si="10">B24*E24</f>
+        <f t="shared" ref="F24" si="12">B24*E24</f>
         <v>16</v>
       </c>
       <c r="G24" s="4">
-        <f>C24*E24</f>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="H24" s="4">
-        <f>D24*E24</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
     </row>
@@ -3591,15 +3813,15 @@
         <v>8</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" ref="F25:F36" si="11">B25*E25</f>
+        <f t="shared" ref="F25:F40" si="13">B25*E25</f>
         <v>16</v>
       </c>
       <c r="G25" s="4">
-        <f>C25*E25</f>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="H25" s="4">
-        <f>D25*E25</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
     </row>
@@ -3620,15 +3842,15 @@
         <v>2</v>
       </c>
       <c r="F26" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="G26" s="4">
-        <f>C26*E26</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H26" s="4">
-        <f>D26*E26</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -3649,15 +3871,15 @@
         <v>3</v>
       </c>
       <c r="F27" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="G27" s="4">
-        <f>C27*E27</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="H27" s="4">
-        <f>D27*E27</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -3678,15 +3900,15 @@
         <v>2</v>
       </c>
       <c r="F28" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="G28" s="4">
-        <f>C28*E28</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H28" s="4">
-        <f>D28*E28</f>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
     </row>
@@ -3707,15 +3929,15 @@
         <v>2</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="G29" s="4">
-        <f>C29*E29</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H29" s="4">
-        <f>D29*E29</f>
+        <f t="shared" si="7"/>
         <v>0.1</v>
       </c>
     </row>
@@ -3736,15 +3958,15 @@
         <v>4</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="G30" s="4">
-        <f>C30*E30</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H30" s="4">
-        <f>D30*E30</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3765,15 +3987,15 @@
         <v>4</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
       <c r="G31" s="4">
-        <f>C31*E31</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H31" s="4">
-        <f>D31*E31</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3794,15 +4016,15 @@
         <v>3</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="G32" s="4">
-        <f>C32*E32</f>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="H32" s="4">
-        <f>D32*E32</f>
+        <f t="shared" si="7"/>
         <v>0.15000000000000002</v>
       </c>
     </row>
@@ -3823,15 +4045,15 @@
         <v>3</v>
       </c>
       <c r="F33" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="G33" s="4">
-        <f>C33*E33</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="H33" s="4">
-        <f>D33*E33</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -3852,15 +4074,15 @@
         <v>3</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="G34" s="4">
-        <f>C34*E34</f>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
       <c r="H34" s="4">
-        <f>D34*E34</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -3881,15 +4103,15 @@
         <v>3</v>
       </c>
       <c r="F35" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
       <c r="G35" s="4">
-        <f>C35*E35</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="H35" s="4">
-        <f>D35*E35</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -3910,88 +4132,234 @@
         <v>2</v>
       </c>
       <c r="F36" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>4</v>
       </c>
       <c r="G36" s="4">
-        <f>C36*E36</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="H36" s="4">
-        <f>D36*E36</f>
+        <f t="shared" si="7"/>
         <v>0.1</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="5"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="A37" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="4">
+        <v>4</v>
+      </c>
+      <c r="C37" s="4">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="E37" s="4">
+        <v>3</v>
+      </c>
+      <c r="F37" s="4">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="G37" s="4">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="H37" s="4">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="4">
+        <v>8</v>
+      </c>
+      <c r="C38" s="4">
+        <v>32</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4">
+        <v>4</v>
+      </c>
+      <c r="F38" s="4">
+        <f t="shared" si="13"/>
+        <v>32</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="6"/>
+        <v>128</v>
+      </c>
+      <c r="H38" s="4">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="4">
+        <v>2</v>
+      </c>
+      <c r="C39" s="4">
+        <v>4</v>
+      </c>
+      <c r="D39" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E39" s="4">
+        <v>3</v>
+      </c>
+      <c r="F39" s="4">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="G39" s="4">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="H39" s="4">
+        <f t="shared" si="7"/>
+        <v>0.30000000000000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="4">
+        <v>4</v>
+      </c>
+      <c r="C40" s="4">
+        <v>8</v>
+      </c>
+      <c r="D40" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="4">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" si="7"/>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="4">
+        <v>4</v>
+      </c>
+      <c r="C41" s="4">
+        <v>8</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="4">
+        <v>3</v>
+      </c>
+      <c r="F41" s="4">
+        <f t="shared" ref="F41" si="14">B41*E41</f>
+        <v>12</v>
+      </c>
+      <c r="G41" s="4">
+        <f t="shared" ref="G41" si="15">C41*E41</f>
+        <v>24</v>
+      </c>
+      <c r="H41" s="4">
+        <f t="shared" ref="H41" si="16">D41*E41</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="5"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F38" s="4">
-        <f>SUM(F2:F37)</f>
-        <v>596</v>
-      </c>
-      <c r="G38" s="4">
-        <f>SUM(G2:G37)</f>
-        <v>1932</v>
-      </c>
-      <c r="H38" s="6">
-        <f>ROUNDUP(SUM(H2:H37),0)</f>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
-      <c r="A39" s="4" t="s">
+      <c r="F43" s="4">
+        <f>SUM(F2:F42)</f>
+        <v>670</v>
+      </c>
+      <c r="G43" s="4">
+        <f>SUM(G2:G42)</f>
+        <v>2144</v>
+      </c>
+      <c r="H43" s="6">
+        <f>ROUNDUP(SUM(H2:H42),0)</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B44" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F39" s="4">
-        <f>ROUNDUP(F38*1.3,0)</f>
-        <v>775</v>
-      </c>
-      <c r="G39" s="4">
-        <f>ROUNDUP(G38*1.3,0)</f>
-        <v>2512</v>
-      </c>
-      <c r="H39" s="4">
-        <f>ROUNDUP(H38*1.3,0)</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="16.5">
-      <c r="L42" s="3"/>
+      <c r="F44" s="4">
+        <f>ROUNDUP(F43*1.3,0)</f>
+        <v>871</v>
+      </c>
+      <c r="G44" s="4">
+        <f>ROUNDUP(G43*1.3,0)</f>
+        <v>2788</v>
+      </c>
+      <c r="H44" s="4">
+        <f>ROUNDUP(H43*1.3,0)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="16.5">
+      <c r="A47" s="37"/>
+      <c r="L47" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4001,4 +4369,77 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A0E402-42AA-4043-8BC8-17CD8529E993}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="39">
+        <v>43.9</v>
+      </c>
+      <c r="B1" s="40">
+        <f>A1*2</f>
+        <v>87.8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>42.44</v>
+      </c>
+      <c r="B2" s="40">
+        <f t="shared" ref="B2:B7" si="0">A2*2</f>
+        <v>84.88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>40.340000000000003</v>
+      </c>
+      <c r="B3" s="40">
+        <f t="shared" si="0"/>
+        <v>80.680000000000007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>37.450000000000003</v>
+      </c>
+      <c r="B4" s="40">
+        <f t="shared" si="0"/>
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>33.56</v>
+      </c>
+      <c r="B5" s="40">
+        <f t="shared" si="0"/>
+        <v>67.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>28.32</v>
+      </c>
+      <c r="B6" s="40">
+        <f t="shared" si="0"/>
+        <v>56.64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>20.68</v>
+      </c>
+      <c r="B7" s="40">
+        <f t="shared" si="0"/>
+        <v>41.36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083FBC0B-766D-427B-A564-B9D39C5EB32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94449434-FCCF-49BD-BCFE-510F07649C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Нагрузка по категориям" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Гео-поиск" sheetId="6" r:id="rId6"/>
     <sheet name="Расчет параметров" sheetId="7" r:id="rId7"/>
     <sheet name="Расчет ресурсов" sheetId="8" r:id="rId8"/>
-    <sheet name="Лист1" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="Лист1" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kfeok\k.feoktistov-SD\doc\рассчет\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94449434-FCCF-49BD-BCFE-510F07649C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F56C49-B1DC-4B37-A741-A2B9C8877AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Нагрузка по категориям" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,20 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -824,6 +838,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -842,32 +882,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -888,9 +902,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -928,7 +942,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1034,7 +1048,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1176,7 +1190,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1202,16 +1216,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="4"/>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31" t="s">
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
@@ -1927,10 +1941,10 @@
         <v>34</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="31">
+      <c r="C5" s="29">
         <v>3</v>
       </c>
-      <c r="D5" s="31"/>
+      <c r="D5" s="29"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -1979,10 +1993,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="31">
+      <c r="C9" s="29">
         <v>400</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="29"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
@@ -2050,10 +2064,10 @@
         <v>39</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="32">
+      <c r="C3" s="30">
         <v>0.1</v>
       </c>
-      <c r="D3" s="33"/>
+      <c r="D3" s="31"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
@@ -2074,10 +2088,10 @@
         <v>37</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="31">
+      <c r="C5" s="29">
         <v>200</v>
       </c>
-      <c r="D5" s="31"/>
+      <c r="D5" s="29"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -2180,10 +2194,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30">
       <c r="A1" s="4"/>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="34"/>
+      <c r="C1" s="32"/>
       <c r="D1" s="9" t="s">
         <v>43</v>
       </c>
@@ -2410,7 +2424,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="33" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="17">
@@ -2440,14 +2454,14 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="35"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="17">
         <v>20</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
@@ -2918,7 +2932,7 @@
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="26" t="s">
         <v>157</v>
       </c>
       <c r="B28" s="17">
@@ -2948,7 +2962,7 @@
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="26" t="s">
         <v>158</v>
       </c>
       <c r="B29" s="17">
@@ -2978,7 +2992,7 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="26" t="s">
         <v>151</v>
       </c>
       <c r="B30" s="17">
@@ -3008,7 +3022,7 @@
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="26" t="s">
         <v>152</v>
       </c>
       <c r="B31" s="17">
@@ -3038,7 +3052,7 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="26" t="s">
         <v>153</v>
       </c>
       <c r="B32" s="17">
@@ -3068,7 +3082,7 @@
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="26" t="s">
         <v>154</v>
       </c>
       <c r="B33" s="17">
@@ -3425,16 +3439,16 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="37"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
@@ -3495,16 +3509,16 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="30"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
@@ -3839,19 +3853,19 @@
         <v>0.5</v>
       </c>
       <c r="E26" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="4">
         <f t="shared" si="13"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4317,11 +4331,11 @@
       </c>
       <c r="F43" s="4">
         <f>SUM(F2:F42)</f>
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="G43" s="4">
         <f>SUM(G2:G42)</f>
-        <v>2144</v>
+        <v>2152</v>
       </c>
       <c r="H43" s="6">
         <f>ROUNDUP(SUM(H2:H42),0)</f>
@@ -4346,11 +4360,11 @@
       </c>
       <c r="F44" s="4">
         <f>ROUNDUP(F43*1.3,0)</f>
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="G44" s="4">
         <f>ROUNDUP(G43*1.3,0)</f>
-        <v>2788</v>
+        <v>2798</v>
       </c>
       <c r="H44" s="4">
         <f>ROUNDUP(H43*1.3,0)</f>
@@ -4358,7 +4372,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="16.5">
-      <c r="A47" s="37"/>
+      <c r="A47" s="25"/>
       <c r="L47" s="3"/>
     </row>
   </sheetData>
@@ -4377,10 +4391,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="39">
+      <c r="A1" s="27">
         <v>43.9</v>
       </c>
-      <c r="B1" s="40">
+      <c r="B1" s="28">
         <f>A1*2</f>
         <v>87.8</v>
       </c>
@@ -4389,7 +4403,7 @@
       <c r="A2">
         <v>42.44</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B2" s="28">
         <f t="shared" ref="B2:B7" si="0">A2*2</f>
         <v>84.88</v>
       </c>
@@ -4398,7 +4412,7 @@
       <c r="A3">
         <v>40.340000000000003</v>
       </c>
-      <c r="B3" s="40">
+      <c r="B3" s="28">
         <f t="shared" si="0"/>
         <v>80.680000000000007</v>
       </c>
@@ -4407,7 +4421,7 @@
       <c r="A4">
         <v>37.450000000000003</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4" s="28">
         <f t="shared" si="0"/>
         <v>74.900000000000006</v>
       </c>
@@ -4416,7 +4430,7 @@
       <c r="A5">
         <v>33.56</v>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="28">
         <f t="shared" si="0"/>
         <v>67.12</v>
       </c>
@@ -4425,7 +4439,7 @@
       <c r="A6">
         <v>28.32</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="28">
         <f t="shared" si="0"/>
         <v>56.64</v>
       </c>
@@ -4434,7 +4448,7 @@
       <c r="A7">
         <v>20.68</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="28">
         <f t="shared" si="0"/>
         <v>41.36</v>
       </c>

--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F56C49-B1DC-4B37-A741-A2B9C8877AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E5000D-AC63-464C-965C-7817275AB4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Нагрузка по категориям" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="Гео-поиск" sheetId="6" r:id="rId6"/>
     <sheet name="Расчет параметров" sheetId="7" r:id="rId7"/>
     <sheet name="Расчет ресурсов" sheetId="8" r:id="rId8"/>
-    <sheet name="Лист1" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="168">
   <si>
     <t>Категория пользователей</t>
   </si>
@@ -647,6 +646,18 @@
   </si>
   <si>
     <t>1 инстанс = 8 000 RPS</t>
+  </si>
+  <si>
+    <t>- входного слоя</t>
+  </si>
+  <si>
+    <t>- внешних интеграций</t>
+  </si>
+  <si>
+    <t>- служб доставки</t>
+  </si>
+  <si>
+    <t>2 инстанс = ~2 500 RPS</t>
   </si>
 </sst>
 </file>
@@ -844,8 +855,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -881,6 +893,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1216,16 +1231,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="4"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29" t="s">
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
@@ -1941,10 +1956,10 @@
         <v>34</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <v>3</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="28"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -1993,10 +2008,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="29">
+      <c r="C9" s="28">
         <v>400</v>
       </c>
-      <c r="D9" s="29"/>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
@@ -2064,10 +2079,10 @@
         <v>39</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="30">
+      <c r="C3" s="29">
         <v>0.1</v>
       </c>
-      <c r="D3" s="31"/>
+      <c r="D3" s="30"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
@@ -2088,10 +2103,10 @@
         <v>37</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <v>200</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="28"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -2177,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEACBF24-690E-480A-A550-EDA8CDE0ADBA}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
@@ -2194,10 +2209,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30">
       <c r="A1" s="4"/>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="32"/>
+      <c r="C1" s="31"/>
       <c r="D1" s="9" t="s">
         <v>43</v>
       </c>
@@ -2424,7 +2439,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="17">
@@ -2454,14 +2469,14 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="33"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="17">
         <v>20</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="33"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
@@ -2472,35 +2487,10 @@
       <c r="A12" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="B12" s="17">
-        <v>50000</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E12" s="17">
-        <v>5000</v>
-      </c>
-      <c r="F12" s="9">
-        <v>1.5</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" s="19">
-        <f t="shared" ref="H12:H30" si="0">B12/E12*F12</f>
-        <v>15</v>
-      </c>
-      <c r="I12" s="9">
-        <v>15</v>
-      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="23" t="s">
-        <v>116</v>
+      <c r="A13" s="15" t="s">
+        <v>164</v>
       </c>
       <c r="B13" s="17">
         <v>50000</v>
@@ -2509,630 +2499,720 @@
         <v>54</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E13" s="17">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F13" s="9">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H13" s="19">
-        <f t="shared" si="0"/>
-        <v>3.25</v>
+        <f>B13/E13*F13</f>
+        <v>15</v>
       </c>
       <c r="I13" s="9">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="23" t="s">
-        <v>117</v>
+      <c r="A14" s="15" t="s">
+        <v>165</v>
       </c>
       <c r="B14" s="17">
-        <v>250</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>52</v>
+        <v>5000</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>54</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="E14" s="17">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="F14" s="9">
         <v>1.5</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="19">
+        <f>B14/E14*F14</f>
+        <v>3</v>
+      </c>
+      <c r="I14" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B15" s="17">
+        <v>1000</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" s="17">
+        <v>2500</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="19">
+        <f>B15/E15*F15</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="I15" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="17">
+        <v>50000</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="17">
+        <v>20000</v>
+      </c>
+      <c r="F16" s="9">
+        <v>1.3</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H16" s="19">
+        <f t="shared" ref="H12:H33" si="0">B16/E16*F16</f>
+        <v>3.25</v>
+      </c>
+      <c r="I16" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="17">
+        <v>250</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="17">
+        <v>200</v>
+      </c>
+      <c r="F17" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="19">
         <f t="shared" si="0"/>
         <v>1.875</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I17" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="23" t="s">
+    <row r="18" spans="1:9">
+      <c r="A18" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B18" s="17">
         <v>500</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C18" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E18" s="17">
         <v>1000</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F18" s="9">
         <v>1.5</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H18" s="19">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I18" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="23" t="s">
+    <row r="19" spans="1:9">
+      <c r="A19" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B19" s="17">
         <v>250</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C19" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E19" s="17">
         <v>100</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F19" s="9">
         <v>1.5</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H19" s="19">
         <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
-      <c r="I16" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="23" t="s">
+      <c r="I19" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B20" s="17">
         <v>250</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C20" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E20" s="17">
         <v>100</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F20" s="9">
         <v>1.5</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="19">
+      <c r="H20" s="19">
         <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
-      <c r="I17" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="23" t="s">
+      <c r="I20" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B21" s="17">
         <v>10000</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C21" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E21" s="17">
         <v>2000</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F21" s="9">
         <v>1.5</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="19">
+      <c r="H21" s="19">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I21" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="23" t="s">
+    <row r="22" spans="1:9">
+      <c r="A22" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B22" s="17">
         <v>5000</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C22" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E22" s="17">
         <v>1000</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F22" s="9">
         <v>1.5</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G22" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H19" s="19">
+      <c r="H22" s="19">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I22" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="23" t="s">
+    <row r="23" spans="1:9">
+      <c r="A23" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B23" s="17">
         <v>10000</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C23" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E23" s="17">
         <v>2000</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F23" s="9">
         <v>1.5</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G23" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H23" s="19">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I23" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="23" t="s">
+    <row r="24" spans="1:9">
+      <c r="A24" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B24" s="17">
         <v>1000</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C24" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E24" s="17">
         <v>2000</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F24" s="9">
         <v>1.5</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H24" s="19">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I24" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="23" t="s">
+    <row r="25" spans="1:9">
+      <c r="A25" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B25" s="17">
         <v>100000</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C25" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E25" s="17">
         <v>50000</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F25" s="9">
         <v>1.5</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G25" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H25" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I25" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="23" t="s">
+    <row r="26" spans="1:9">
+      <c r="A26" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B26" s="17">
         <v>10000</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C26" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E26" s="17">
         <v>8000</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F26" s="9">
         <v>1.5</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G26" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H23" s="19">
+      <c r="H26" s="19">
         <f t="shared" si="0"/>
         <v>1.875</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I26" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="23" t="s">
+    <row r="27" spans="1:9">
+      <c r="A27" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B27" s="17">
         <v>5000</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C27" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E27" s="17">
         <v>2000</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F27" s="9">
         <v>1.5</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G27" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H24" s="19">
+      <c r="H27" s="19">
         <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
-      <c r="I24" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="23" t="s">
+      <c r="I27" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B28" s="17">
         <v>7500</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C28" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E28" s="17">
         <v>3000</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F28" s="9">
         <v>1.5</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G28" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H28" s="19">
         <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
-      <c r="I25" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="23" t="s">
+      <c r="I28" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B29" s="17">
         <v>5000</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C29" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D29" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E29" s="17">
         <v>2500</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F29" s="9">
         <v>1.3</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G29" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="19">
+      <c r="H29" s="19">
         <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I29" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="23" t="s">
+    <row r="30" spans="1:9">
+      <c r="A30" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="9"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="26" t="s">
+      <c r="B30" s="17"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B31" s="17">
         <v>750</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D31" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E31" s="17">
         <v>1500</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F31" s="9">
         <v>1.5</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G31" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H28" s="19">
+      <c r="H31" s="19">
         <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I31" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="26" t="s">
+    <row r="32" spans="1:9">
+      <c r="A32" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B32" s="17">
         <v>1000</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C32" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D32" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E32" s="17">
         <v>500</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F32" s="9">
         <v>1.5</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G32" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H32" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I32" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="26" t="s">
+    <row r="33" spans="1:9">
+      <c r="A33" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B33" s="17">
         <v>500</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C33" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D33" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E33" s="17">
         <v>1000</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F33" s="9">
         <v>1.3</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G33" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H33" s="19">
         <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I33" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="26" t="s">
+    <row r="34" spans="1:9">
+      <c r="A34" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B34" s="17">
         <v>250</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C34" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E34" s="17">
         <v>200</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F34" s="9">
         <v>1.5</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G34" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H31" s="19">
-        <f t="shared" ref="H31:H33" si="1">B31/E31*F31</f>
+      <c r="H34" s="19">
+        <f t="shared" ref="H34:H36" si="1">B34/E34*F34</f>
         <v>1.875</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I34" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="26" t="s">
+    <row r="35" spans="1:9">
+      <c r="A35" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="B32" s="17">
+      <c r="B35" s="17">
         <v>1000</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C35" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D35" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E35" s="17">
         <v>500</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F35" s="9">
         <v>1.3</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G35" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H32" s="19">
+      <c r="H35" s="19">
         <f t="shared" si="1"/>
         <v>2.6</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I35" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="26" t="s">
+    <row r="36" spans="1:9">
+      <c r="A36" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B36" s="17">
         <v>10000</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C36" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D36" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E36" s="17">
         <v>8000</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F36" s="9">
         <v>1.5</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G36" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="H33" s="19">
+      <c r="H36" s="19">
         <f t="shared" si="1"/>
         <v>1.875</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I36" s="9">
         <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3150,7 +3230,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F55A25-67AE-4582-B6E5-DF4CB5C7DF4D}">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -3439,16 +3519,16 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="37"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
@@ -3509,16 +3589,16 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="40"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
@@ -3541,11 +3621,11 @@
         <v>96</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" ref="G15:G40" si="6">C15*E15</f>
+        <f t="shared" ref="G15:G43" si="6">C15*E15</f>
         <v>192</v>
       </c>
       <c r="H15" s="4">
-        <f t="shared" ref="H15:H40" si="7">D15*E15</f>
+        <f t="shared" ref="H15:H43" si="7">D15*E15</f>
         <v>24</v>
       </c>
     </row>
@@ -3582,121 +3662,97 @@
       <c r="A17" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="4">
-        <v>4</v>
-      </c>
-      <c r="C17" s="4">
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="4">
+        <v>4</v>
+      </c>
+      <c r="C18" s="4">
         <v>8</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D18" s="4">
         <v>0.2</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E18" s="9">
         <v>15</v>
       </c>
-      <c r="F17" s="4">
-        <f t="shared" si="8"/>
+      <c r="F18" s="4">
+        <f>B18*E18</f>
         <v>60</v>
       </c>
-      <c r="G17" s="4">
-        <f t="shared" si="6"/>
+      <c r="G18" s="4">
+        <f>C18*E18</f>
         <v>120</v>
       </c>
-      <c r="H17" s="4">
-        <f t="shared" si="7"/>
+      <c r="H18" s="4">
+        <f>D18*E18</f>
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="4">
-        <v>2</v>
-      </c>
-      <c r="C18" s="4">
-        <v>4</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="E18" s="9">
-        <v>4</v>
-      </c>
-      <c r="F18" s="4">
-        <f t="shared" ref="F18" si="9">B18*E18</f>
+    <row r="19" spans="1:8">
+      <c r="A19" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="4">
+        <v>4</v>
+      </c>
+      <c r="C19" s="4">
         <v>8</v>
       </c>
-      <c r="G18" s="4">
-        <f t="shared" si="6"/>
-        <v>16</v>
-      </c>
-      <c r="H18" s="4">
-        <f t="shared" si="7"/>
+      <c r="D19" s="4">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="4">
-        <v>2</v>
-      </c>
-      <c r="C19" s="4">
-        <v>4</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0.05</v>
-      </c>
       <c r="E19" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" ref="F19:F22" si="10">B19*E19</f>
-        <v>4</v>
+        <f t="shared" ref="F19:F20" si="9">B19*E19</f>
+        <v>12</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G19:G20" si="10">C19*E19</f>
+        <v>24</v>
+      </c>
+      <c r="H19" s="4">
+        <f t="shared" ref="H19:H20" si="11">D19*E19</f>
+        <v>0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="4">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4">
         <v>8</v>
       </c>
-      <c r="H19" s="4">
-        <f t="shared" si="7"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="4">
-        <v>2</v>
-      </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
       <c r="D20" s="4">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="E20" s="9">
         <v>2</v>
       </c>
       <c r="F20" s="4">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="G20" s="4">
         <f t="shared" si="10"/>
-        <v>4</v>
-      </c>
-      <c r="G20" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="7"/>
-        <v>0.1</v>
+        <f t="shared" si="11"/>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="23" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B21" s="4">
         <v>2</v>
@@ -3711,7 +3767,7 @@
         <v>4</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="F21" si="12">B21*E21</f>
         <v>8</v>
       </c>
       <c r="G21" s="4">
@@ -3725,7 +3781,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B22" s="4">
         <v>2</v>
@@ -3737,53 +3793,53 @@
         <v>0.05</v>
       </c>
       <c r="E22" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="10"/>
-        <v>8</v>
+        <f t="shared" ref="F22:F25" si="13">B22*E22</f>
+        <v>4</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B23" s="4">
         <v>2</v>
       </c>
       <c r="C23" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4">
         <v>0.05</v>
       </c>
       <c r="E23" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F23" s="4">
-        <f t="shared" ref="F23" si="11">B23*E23</f>
-        <v>16</v>
+        <f t="shared" si="13"/>
+        <v>4</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="23" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B24" s="4">
         <v>2</v>
@@ -3795,24 +3851,24 @@
         <v>0.05</v>
       </c>
       <c r="E24" s="9">
+        <v>4</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="13"/>
         <v>8</v>
-      </c>
-      <c r="F24" s="4">
-        <f t="shared" ref="F24" si="12">B24*E24</f>
-        <v>16</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="23" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B25" s="4">
         <v>2</v>
@@ -3824,102 +3880,102 @@
         <v>0.05</v>
       </c>
       <c r="E25" s="9">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4">
+        <f t="shared" si="13"/>
         <v>8</v>
-      </c>
-      <c r="F25" s="4">
-        <f t="shared" ref="F25:F40" si="13">B25*E25</f>
-        <v>16</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="23" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B26" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" s="4">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E26" s="9">
         <v>8</v>
       </c>
-      <c r="D26" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E26" s="9">
-        <v>3</v>
-      </c>
       <c r="F26" s="4">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <f t="shared" ref="F26" si="14">B26*E26</f>
+        <v>16</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="7"/>
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="23" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B27" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="4">
+        <v>4</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E27" s="9">
         <v>8</v>
       </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="9">
-        <v>3</v>
-      </c>
       <c r="F27" s="4">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <f t="shared" ref="F27" si="15">B27*E27</f>
+        <v>16</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="23" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B28" s="4">
         <v>2</v>
       </c>
       <c r="C28" s="4">
+        <v>4</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E28" s="9">
         <v>8</v>
       </c>
-      <c r="D28" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="9">
-        <v>2</v>
-      </c>
       <c r="F28" s="4">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <f t="shared" ref="F28:F43" si="16">B28*E28</f>
+        <v>16</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="7"/>
@@ -3928,81 +3984,81 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="23" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B29" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D29" s="4">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="E29" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="4">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>12</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="23" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B30" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C30" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D30" s="4">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="E30" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="4">
-        <f t="shared" si="13"/>
-        <v>8</v>
+        <f t="shared" si="16"/>
+        <v>12</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="23" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B31" s="4">
         <v>2</v>
       </c>
       <c r="C31" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D31" s="4">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="E31" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" s="4">
-        <f t="shared" si="13"/>
-        <v>8</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="6"/>
@@ -4010,244 +4066,244 @@
       </c>
       <c r="H31" s="4">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="5" t="s">
-        <v>142</v>
+      <c r="A32" s="23" t="s">
+        <v>143</v>
       </c>
       <c r="B32" s="4">
         <v>2</v>
       </c>
       <c r="C32" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" s="4">
         <v>0.05</v>
       </c>
-      <c r="E32" s="4">
-        <v>3</v>
+      <c r="E32" s="9">
+        <v>2</v>
       </c>
       <c r="F32" s="4">
-        <f t="shared" si="13"/>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
-        <v>0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="5" t="s">
-        <v>145</v>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="23" t="s">
+        <v>138</v>
       </c>
       <c r="B33" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="4">
+        <v>4</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="E33" s="9">
+        <v>4</v>
+      </c>
+      <c r="F33" s="4">
+        <f t="shared" si="16"/>
         <v>8</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="4">
-        <v>3</v>
-      </c>
-      <c r="F33" s="4">
-        <f t="shared" si="13"/>
-        <v>12</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="5" t="s">
-        <v>146</v>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="23" t="s">
+        <v>140</v>
       </c>
       <c r="B34" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C34" s="4">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D34" s="4">
-        <v>2</v>
-      </c>
-      <c r="E34" s="4">
-        <v>3</v>
+        <v>0.05</v>
+      </c>
+      <c r="E34" s="9">
+        <v>4</v>
       </c>
       <c r="F34" s="4">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <f t="shared" si="16"/>
+        <v>8</v>
       </c>
       <c r="G34" s="4">
         <f t="shared" si="6"/>
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B35" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D35" s="4">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="E35" s="4">
         <v>3</v>
       </c>
       <c r="F35" s="4">
-        <f t="shared" si="13"/>
-        <v>12</v>
+        <f t="shared" si="16"/>
+        <v>6</v>
       </c>
       <c r="G35" s="4">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
+        <v>0.15000000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="4">
+        <v>4</v>
+      </c>
+      <c r="C36" s="4">
+        <v>8</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" s="4">
-        <v>2</v>
-      </c>
-      <c r="C36" s="4">
-        <v>2</v>
-      </c>
-      <c r="D36" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="E36" s="4">
-        <v>2</v>
-      </c>
       <c r="F36" s="4">
-        <f t="shared" si="13"/>
-        <v>4</v>
+        <f t="shared" si="16"/>
+        <v>12</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B37" s="4">
         <v>4</v>
       </c>
       <c r="C37" s="4">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D37" s="4">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
         <v>3</v>
       </c>
       <c r="F37" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B38" s="4">
+        <v>4</v>
+      </c>
+      <c r="C38" s="4">
         <v>8</v>
-      </c>
-      <c r="C38" s="4">
-        <v>32</v>
       </c>
       <c r="D38" s="4">
         <v>1</v>
       </c>
       <c r="E38" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" s="4">
-        <f t="shared" si="13"/>
-        <v>32</v>
+        <f t="shared" si="16"/>
+        <v>12</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="6"/>
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B39" s="4">
         <v>2</v>
       </c>
       <c r="C39" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" s="4">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E39" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39" s="4">
-        <f t="shared" si="13"/>
-        <v>6</v>
+        <f t="shared" si="16"/>
+        <v>4</v>
       </c>
       <c r="G39" s="4">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
-        <v>0.30000000000000004</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40" s="4">
         <v>4</v>
@@ -4256,13 +4312,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="4">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E40" s="4">
         <v>3</v>
       </c>
       <c r="F40" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>12</v>
       </c>
       <c r="G40" s="4">
@@ -4271,109 +4327,196 @@
       </c>
       <c r="H40" s="4">
         <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="4">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4">
+        <v>32</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4">
+        <v>4</v>
+      </c>
+      <c r="F41" s="4">
+        <f t="shared" si="16"/>
+        <v>32</v>
+      </c>
+      <c r="G41" s="4">
+        <f t="shared" si="6"/>
+        <v>128</v>
+      </c>
+      <c r="H41" s="4">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="4">
+        <v>2</v>
+      </c>
+      <c r="C42" s="4">
+        <v>4</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>3</v>
+      </c>
+      <c r="F42" s="4">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="7"/>
+        <v>0.30000000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" s="4">
+        <v>4</v>
+      </c>
+      <c r="C43" s="4">
+        <v>8</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="4">
+        <v>3</v>
+      </c>
+      <c r="F43" s="4">
+        <f t="shared" si="16"/>
+        <v>12</v>
+      </c>
+      <c r="G43" s="4">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="H43" s="4">
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
-      <c r="A41" s="5" t="s">
+    <row r="44" spans="1:8">
+      <c r="A44" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B41" s="4">
-        <v>4</v>
-      </c>
-      <c r="C41" s="4">
+      <c r="B44" s="4">
+        <v>4</v>
+      </c>
+      <c r="C44" s="4">
         <v>8</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D44" s="4">
         <v>0.5</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E44" s="4">
         <v>3</v>
       </c>
-      <c r="F41" s="4">
-        <f t="shared" ref="F41" si="14">B41*E41</f>
+      <c r="F44" s="4">
+        <f t="shared" ref="F44" si="17">B44*E44</f>
         <v>12</v>
       </c>
-      <c r="G41" s="4">
-        <f t="shared" ref="G41" si="15">C41*E41</f>
+      <c r="G44" s="4">
+        <f t="shared" ref="G44" si="18">C44*E44</f>
         <v>24</v>
       </c>
-      <c r="H41" s="4">
-        <f t="shared" ref="H41" si="16">D41*E41</f>
+      <c r="H44" s="4">
+        <f t="shared" ref="H44" si="19">D44*E44</f>
         <v>1.5</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="5"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="4" t="s">
+    <row r="45" spans="1:8">
+      <c r="A45" s="5"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B46" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F43" s="4">
-        <f>SUM(F2:F42)</f>
-        <v>674</v>
-      </c>
-      <c r="G43" s="4">
-        <f>SUM(G2:G42)</f>
-        <v>2152</v>
-      </c>
-      <c r="H43" s="6">
-        <f>ROUNDUP(SUM(H2:H42),0)</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="4" t="s">
+      <c r="F46" s="4">
+        <f>SUM(F2:F45)</f>
+        <v>694</v>
+      </c>
+      <c r="G46" s="4">
+        <f>SUM(G2:G45)</f>
+        <v>2192</v>
+      </c>
+      <c r="H46" s="6">
+        <f>ROUNDUP(SUM(H2:H45),0)</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="4">
-        <f>ROUNDUP(F43*1.3,0)</f>
-        <v>877</v>
-      </c>
-      <c r="G44" s="4">
-        <f>ROUNDUP(G43*1.3,0)</f>
-        <v>2798</v>
-      </c>
-      <c r="H44" s="4">
-        <f>ROUNDUP(H43*1.3,0)</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="16.5">
-      <c r="A47" s="25"/>
-      <c r="L47" s="3"/>
+      <c r="F47" s="4">
+        <f>ROUNDUP(F46*1.3,0)</f>
+        <v>903</v>
+      </c>
+      <c r="G47" s="4">
+        <f>ROUNDUP(G46*1.3,0)</f>
+        <v>2850</v>
+      </c>
+      <c r="H47" s="4">
+        <f>ROUNDUP(H46*1.3,0)</f>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="16.5">
+      <c r="A50" s="25"/>
+      <c r="L50" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4383,77 +4526,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1A0E402-42AA-4043-8BC8-17CD8529E993}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="27">
-        <v>43.9</v>
-      </c>
-      <c r="B1" s="28">
-        <f>A1*2</f>
-        <v>87.8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>42.44</v>
-      </c>
-      <c r="B2" s="28">
-        <f t="shared" ref="B2:B7" si="0">A2*2</f>
-        <v>84.88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>40.340000000000003</v>
-      </c>
-      <c r="B3" s="28">
-        <f t="shared" si="0"/>
-        <v>80.680000000000007</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>37.450000000000003</v>
-      </c>
-      <c r="B4" s="28">
-        <f t="shared" si="0"/>
-        <v>74.900000000000006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>33.56</v>
-      </c>
-      <c r="B5" s="28">
-        <f t="shared" si="0"/>
-        <v>67.12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>28.32</v>
-      </c>
-      <c r="B6" s="28">
-        <f t="shared" si="0"/>
-        <v>56.64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>20.68</v>
-      </c>
-      <c r="B7" s="28">
-        <f t="shared" si="0"/>
-        <v>41.36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/doc/рассчет/Расчет нагрузки.xlsx
+++ b/doc/рассчет/Расчет нагрузки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOTT\Documents\Учеба\System Design\GIT\k.feoktistov-SD\doc\рассчет\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E5000D-AC63-464C-965C-7817275AB4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E314B4-EAF9-41A8-80B4-1DD27BDC8521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{548C2066-4916-4BCB-AD8A-EB90AA9710FB}"/>
   </bookViews>
@@ -858,6 +858,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -893,9 +896,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1231,16 +1231,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="4"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28" t="s">
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
@@ -1956,10 +1956,10 @@
         <v>34</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="28">
+      <c r="C5" s="29">
         <v>3</v>
       </c>
-      <c r="D5" s="28"/>
+      <c r="D5" s="29"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -2008,10 +2008,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <v>400</v>
       </c>
-      <c r="D9" s="28"/>
+      <c r="D9" s="29"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
@@ -2079,10 +2079,10 @@
         <v>39</v>
       </c>
       <c r="B3" s="4"/>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>0.1</v>
       </c>
-      <c r="D3" s="30"/>
+      <c r="D3" s="31"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
@@ -2103,10 +2103,10 @@
         <v>37</v>
       </c>
       <c r="B5" s="4"/>
-      <c r="C5" s="28">
+      <c r="C5" s="29">
         <v>200</v>
       </c>
-      <c r="D5" s="28"/>
+      <c r="D5" s="29"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
@@ -2209,10 +2209,10 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30">
       <c r="A1" s="4"/>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="31"/>
+      <c r="C1" s="32"/>
       <c r="D1" s="9" t="s">
         <v>43</v>
       </c>
@@ -2439,7 +2439,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>49</v>
       </c>
       <c r="B10" s="17">
@@ -2469,14 +2469,14 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="32"/>
+      <c r="A11" s="33"/>
       <c r="B11" s="17">
         <v>20</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="33"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
@@ -2549,7 +2549,7 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="28" t="s">
         <v>166</v>
       </c>
       <c r="B15" s="17">
@@ -2601,7 +2601,7 @@
         <v>60</v>
       </c>
       <c r="H16" s="19">
-        <f t="shared" ref="H12:H33" si="0">B16/E16*F16</f>
+        <f t="shared" ref="H16:H33" si="0">B16/E16*F16</f>
         <v>3.25</v>
       </c>
       <c r="I16" s="9">
@@ -3519,16 +3519,16 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="37"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
@@ -3589,16 +3589,16 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
@@ -3646,7 +3646,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" ref="F16:F17" si="8">B16*E16</f>
+        <f t="shared" ref="F16" si="8">B16*E16</f>
         <v>24</v>
       </c>
       <c r="G16" s="4">
@@ -3722,7 +3722,7 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="28" t="s">
         <v>166</v>
       </c>
       <c r="B20" s="4">
